--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="111">
   <si>
     <t>청약일</t>
   </si>
@@ -124,9 +124,6 @@
     <t>2024-06-10</t>
   </si>
   <si>
-    <t>2024-06-05</t>
-  </si>
-  <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
@@ -190,12 +187,6 @@
     <t>한중엔시에스</t>
   </si>
   <si>
-    <t>라메디텍</t>
-  </si>
-  <si>
-    <t>디비금융스팩12호</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
@@ -235,9 +226,6 @@
     <t>IBK</t>
   </si>
   <si>
-    <t>DB</t>
-  </si>
-  <si>
     <t>신한, 한국</t>
   </si>
   <si>
@@ -356,12 +344,6 @@
   </si>
   <si>
     <t>1000.82 : 1</t>
-  </si>
-  <si>
-    <t>2140 : 1</t>
-  </si>
-  <si>
-    <t>1141.4 : 1</t>
   </si>
   <si>
     <t>120.3 : 1</t>
@@ -722,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -792,16 +774,16 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F2">
         <v>22340000</v>
@@ -810,7 +792,7 @@
         <v>2234000</v>
       </c>
       <c r="H2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I2">
         <v>7300</v>
@@ -819,34 +801,34 @@
         <v>8500</v>
       </c>
       <c r="K2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L2">
         <v>10000</v>
       </c>
       <c r="M2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="S2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -854,16 +836,16 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F3">
         <v>29700000</v>
@@ -872,7 +854,7 @@
         <v>1350000</v>
       </c>
       <c r="H3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I3">
         <v>14000</v>
@@ -881,34 +863,34 @@
         <v>17000</v>
       </c>
       <c r="K3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L3">
         <v>22000</v>
       </c>
       <c r="M3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="S3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -916,16 +898,16 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F4">
         <v>266000000</v>
@@ -934,7 +916,7 @@
         <v>7600000</v>
       </c>
       <c r="H4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I4">
         <v>24000</v>
@@ -943,34 +925,34 @@
         <v>30000</v>
       </c>
       <c r="K4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L4">
         <v>35000</v>
       </c>
       <c r="M4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O4">
         <v>14.47368421052632</v>
       </c>
       <c r="P4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="S4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -978,16 +960,16 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F5">
         <v>12000000</v>
@@ -996,7 +978,7 @@
         <v>6000000</v>
       </c>
       <c r="H5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I5">
         <v>2000</v>
@@ -1005,34 +987,34 @@
         <v>2000</v>
       </c>
       <c r="K5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L5">
         <v>2000</v>
       </c>
       <c r="M5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>88</v>
+      </c>
+      <c r="R5" t="s">
         <v>92</v>
       </c>
-      <c r="Q5" t="s">
-        <v>92</v>
-      </c>
-      <c r="R5" t="s">
-        <v>96</v>
-      </c>
       <c r="S5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1040,10 +1022,10 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1058,7 +1040,7 @@
         <v>4000000</v>
       </c>
       <c r="H6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I6">
         <v>2000</v>
@@ -1067,34 +1049,34 @@
         <v>2000</v>
       </c>
       <c r="K6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L6">
         <v>2000</v>
       </c>
       <c r="M6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="S6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1102,13 +1084,13 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
         <v>24</v>
@@ -1120,7 +1102,7 @@
         <v>1618000</v>
       </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I7">
         <v>6200</v>
@@ -1129,34 +1111,34 @@
         <v>7700</v>
       </c>
       <c r="K7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L7">
         <v>10000</v>
       </c>
       <c r="M7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="S7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1164,16 +1146,16 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F8">
         <v>435000000</v>
@@ -1182,7 +1164,7 @@
         <v>7250000</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I8">
         <v>47000</v>
@@ -1191,34 +1173,34 @@
         <v>60000</v>
       </c>
       <c r="K8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L8">
         <v>60000</v>
       </c>
       <c r="M8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R8" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="S8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1226,16 +1208,16 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F9">
         <v>8000000</v>
@@ -1244,7 +1226,7 @@
         <v>4000000</v>
       </c>
       <c r="H9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I9">
         <v>2000</v>
@@ -1253,34 +1235,34 @@
         <v>2000</v>
       </c>
       <c r="K9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L9">
         <v>2000</v>
       </c>
       <c r="M9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="S9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1288,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
         <v>25</v>
@@ -1306,7 +1288,7 @@
         <v>1810000</v>
       </c>
       <c r="H10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I10">
         <v>9000</v>
@@ -1315,34 +1297,34 @@
         <v>12000</v>
       </c>
       <c r="K10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L10">
         <v>16000</v>
       </c>
       <c r="M10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="S10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1350,13 +1332,13 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
         <v>26</v>
@@ -1368,7 +1350,7 @@
         <v>1330000</v>
       </c>
       <c r="H11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I11">
         <v>36400</v>
@@ -1377,34 +1359,34 @@
         <v>43300</v>
       </c>
       <c r="K11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L11">
         <v>43300</v>
       </c>
       <c r="M11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="S11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1412,16 +1394,16 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
         <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F12">
         <v>43200000</v>
@@ -1430,7 +1412,7 @@
         <v>2400000</v>
       </c>
       <c r="H12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I12">
         <v>11000</v>
@@ -1439,34 +1421,34 @@
         <v>14200</v>
       </c>
       <c r="K12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L12">
         <v>18000</v>
       </c>
       <c r="M12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="S12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1474,16 +1456,16 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F13">
         <v>23800000</v>
@@ -1492,7 +1474,7 @@
         <v>3400000</v>
       </c>
       <c r="H13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I13">
         <v>4500</v>
@@ -1501,34 +1483,34 @@
         <v>5500</v>
       </c>
       <c r="K13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L13">
         <v>7000</v>
       </c>
       <c r="M13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="S13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1536,16 +1518,16 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F14">
         <v>12500000</v>
@@ -1554,7 +1536,7 @@
         <v>6250000</v>
       </c>
       <c r="H14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I14">
         <v>2000</v>
@@ -1563,34 +1545,34 @@
         <v>2000</v>
       </c>
       <c r="K14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L14">
         <v>2000</v>
       </c>
       <c r="M14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="S14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1598,16 +1580,16 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F15">
         <v>23000000</v>
@@ -1616,7 +1598,7 @@
         <v>2000000</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I15">
         <v>7500</v>
@@ -1625,34 +1607,34 @@
         <v>9000</v>
       </c>
       <c r="K15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L15">
         <v>11500</v>
       </c>
       <c r="M15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="S15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1660,10 +1642,10 @@
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
         <v>30</v>
@@ -1678,7 +1660,7 @@
         <v>6450000</v>
       </c>
       <c r="H16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1687,34 +1669,34 @@
         <v>2000</v>
       </c>
       <c r="K16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L16">
         <v>2000</v>
       </c>
       <c r="M16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R16" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="S16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1722,16 +1704,16 @@
         <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F17">
         <v>12000000</v>
@@ -1740,7 +1722,7 @@
         <v>6000000</v>
       </c>
       <c r="H17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1749,34 +1731,34 @@
         <v>2000</v>
       </c>
       <c r="K17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L17">
         <v>2000</v>
       </c>
       <c r="M17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R17" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="S17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1784,10 +1766,10 @@
         <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -1802,7 +1784,7 @@
         <v>7000000</v>
       </c>
       <c r="H18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I18">
         <v>2000</v>
@@ -1811,34 +1793,34 @@
         <v>2000</v>
       </c>
       <c r="K18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L18">
         <v>2000</v>
       </c>
       <c r="M18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R18" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="S18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1846,10 +1828,10 @@
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
         <v>33</v>
@@ -1864,7 +1846,7 @@
         <v>4000000</v>
       </c>
       <c r="H19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I19">
         <v>2000</v>
@@ -1873,34 +1855,34 @@
         <v>2000</v>
       </c>
       <c r="K19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L19">
         <v>2000</v>
       </c>
       <c r="M19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R19" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="S19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -1908,10 +1890,10 @@
         <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
         <v>33</v>
@@ -1926,7 +1908,7 @@
         <v>4750000</v>
       </c>
       <c r="H20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1935,34 +1917,34 @@
         <v>2000</v>
       </c>
       <c r="K20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L20">
         <v>2000</v>
       </c>
       <c r="M20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -1970,10 +1952,10 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
         <v>33</v>
@@ -1988,7 +1970,7 @@
         <v>1300000</v>
       </c>
       <c r="H21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I21">
         <v>10500</v>
@@ -1997,34 +1979,34 @@
         <v>14000</v>
       </c>
       <c r="K21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L21">
         <v>17000</v>
       </c>
       <c r="M21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R21" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="S21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -2032,10 +2014,10 @@
         <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
         <v>33</v>
@@ -2050,7 +2032,7 @@
         <v>1600000</v>
       </c>
       <c r="H22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I22">
         <v>20000</v>
@@ -2059,220 +2041,96 @@
         <v>23500</v>
       </c>
       <c r="K22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L22">
         <v>30000</v>
       </c>
       <c r="M22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R22" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="S22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:20">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="F23">
-        <v>20768000</v>
+        <v>70000002</v>
       </c>
       <c r="G23">
-        <v>1298000</v>
+        <v>23333334</v>
       </c>
       <c r="H23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I23">
-        <v>10400</v>
+        <v>3000</v>
       </c>
       <c r="J23">
-        <v>12700</v>
+        <v>3800</v>
       </c>
       <c r="K23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L23">
-        <v>16000</v>
+        <v>3000</v>
       </c>
       <c r="M23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R23" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="S23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="T23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24">
-        <v>10000000</v>
-      </c>
-      <c r="G24">
-        <v>5000000</v>
-      </c>
-      <c r="H24" t="s">
-        <v>92</v>
-      </c>
-      <c r="I24">
-        <v>2000</v>
-      </c>
-      <c r="J24">
-        <v>2000</v>
-      </c>
-      <c r="K24" t="s">
-        <v>92</v>
-      </c>
-      <c r="L24">
-        <v>2000</v>
-      </c>
-      <c r="M24" t="s">
-        <v>92</v>
-      </c>
-      <c r="N24" t="s">
-        <v>92</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>92</v>
-      </c>
-      <c r="R24" t="s">
-        <v>115</v>
-      </c>
-      <c r="S24" t="s">
-        <v>92</v>
-      </c>
-      <c r="T24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" t="s">
-        <v>91</v>
-      </c>
-      <c r="F25">
-        <v>70000002</v>
-      </c>
-      <c r="G25">
-        <v>23333334</v>
-      </c>
-      <c r="H25" t="s">
-        <v>92</v>
-      </c>
-      <c r="I25">
-        <v>3000</v>
-      </c>
-      <c r="J25">
-        <v>3800</v>
-      </c>
-      <c r="K25" t="s">
-        <v>92</v>
-      </c>
-      <c r="L25">
-        <v>3000</v>
-      </c>
-      <c r="M25" t="s">
-        <v>92</v>
-      </c>
-      <c r="N25" t="s">
-        <v>92</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>92</v>
-      </c>
-      <c r="R25" t="s">
-        <v>116</v>
-      </c>
-      <c r="S25" t="s">
-        <v>92</v>
-      </c>
-      <c r="T25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="105">
   <si>
     <t>청약일</t>
   </si>
@@ -76,6 +76,9 @@
     <t>수수료율</t>
   </si>
   <si>
+    <t>2024-08-01</t>
+  </si>
+  <si>
     <t>2024-07-25</t>
   </si>
   <si>
@@ -121,7 +124,7 @@
     <t>2024-06-11</t>
   </si>
   <si>
-    <t>2024-06-10</t>
+    <t>뱅크웨어글로벌</t>
   </si>
   <si>
     <t>아이빔테크놀로지</t>
@@ -175,30 +178,18 @@
     <t>에이치엠씨제7호스팩</t>
   </si>
   <si>
-    <t>한국제14호스팩</t>
-  </si>
-  <si>
-    <t>미래에셋비전스팩5호</t>
-  </si>
-  <si>
-    <t>씨어스테크놀로지</t>
-  </si>
-  <si>
-    <t>한중엔시에스</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
+    <t>미래</t>
+  </si>
+  <si>
     <t>삼성</t>
   </si>
   <si>
     <t>키움</t>
   </si>
   <si>
-    <t>미래</t>
-  </si>
-  <si>
     <t>NH</t>
   </si>
   <si>
@@ -223,12 +214,12 @@
     <t>현대차</t>
   </si>
   <si>
-    <t>IBK</t>
-  </si>
-  <si>
     <t>신한, 한국</t>
   </si>
   <si>
+    <t>2024-08-06</t>
+  </si>
+  <si>
     <t>2024-07-30</t>
   </si>
   <si>
@@ -253,7 +244,7 @@
     <t>2024-06-21</t>
   </si>
   <si>
-    <t>2024-08-06</t>
+    <t>2024-08-12</t>
   </si>
   <si>
     <t>2024-07-31</t>
@@ -283,6 +274,9 @@
     <t>-</t>
   </si>
   <si>
+    <t>239.19 : 1</t>
+  </si>
+  <si>
     <t>1094.66 : 1</t>
   </si>
   <si>
@@ -332,18 +326,6 @@
   </si>
   <si>
     <t>205.26 : 1</t>
-  </si>
-  <si>
-    <t>333.67 : 1</t>
-  </si>
-  <si>
-    <t>378 : 1</t>
-  </si>
-  <si>
-    <t>1436.96 : 1</t>
-  </si>
-  <si>
-    <t>1000.82 : 1</t>
   </si>
   <si>
     <t>120.3 : 1</t>
@@ -704,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -777,58 +759,58 @@
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F2">
-        <v>22340000</v>
+        <v>22400000</v>
       </c>
       <c r="G2">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I2">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J2">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L2">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="M2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -839,58 +821,58 @@
         <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F3">
-        <v>29700000</v>
+        <v>22340000</v>
       </c>
       <c r="G3">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I3">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J3">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L3">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="M3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -901,58 +883,58 @@
         <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F4">
-        <v>266000000</v>
+        <v>29700000</v>
       </c>
       <c r="G4">
-        <v>7600000</v>
+        <v>1350000</v>
       </c>
       <c r="H4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4">
+        <v>14000</v>
+      </c>
+      <c r="J4">
+        <v>17000</v>
+      </c>
+      <c r="K4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L4">
+        <v>22000</v>
+      </c>
+      <c r="M4" t="s">
+        <v>85</v>
+      </c>
+      <c r="N4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>85</v>
+      </c>
+      <c r="R4" t="s">
         <v>88</v>
       </c>
-      <c r="I4">
-        <v>24000</v>
-      </c>
-      <c r="J4">
-        <v>30000</v>
-      </c>
-      <c r="K4" t="s">
-        <v>88</v>
-      </c>
-      <c r="L4">
-        <v>35000</v>
-      </c>
-      <c r="M4" t="s">
-        <v>88</v>
-      </c>
-      <c r="N4" t="s">
-        <v>88</v>
-      </c>
-      <c r="O4">
-        <v>14.47368421052632</v>
-      </c>
-      <c r="P4" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>88</v>
-      </c>
-      <c r="R4" t="s">
-        <v>91</v>
-      </c>
       <c r="S4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -963,58 +945,58 @@
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F5">
-        <v>12000000</v>
+        <v>266000000</v>
       </c>
       <c r="G5">
-        <v>6000000</v>
+        <v>7600000</v>
       </c>
       <c r="H5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I5">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J5">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="K5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L5">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="M5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>14.47368421052632</v>
       </c>
       <c r="P5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="S5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1025,22 +1007,22 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="F6">
-        <v>8000000</v>
+        <v>12000000</v>
       </c>
       <c r="G6">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I6">
         <v>2000</v>
@@ -1049,34 +1031,34 @@
         <v>2000</v>
       </c>
       <c r="K6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L6">
         <v>2000</v>
       </c>
       <c r="M6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="S6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1087,58 +1069,58 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>16180000</v>
+        <v>8000000</v>
       </c>
       <c r="G7">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I7">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J7">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L7">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="M7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="S7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1149,120 +1131,120 @@
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>435000000</v>
+        <v>16180000</v>
       </c>
       <c r="G8">
-        <v>7250000</v>
+        <v>1618000</v>
       </c>
       <c r="H8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I8">
-        <v>47000</v>
+        <v>6200</v>
       </c>
       <c r="J8">
-        <v>60000</v>
+        <v>7700</v>
       </c>
       <c r="K8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L8">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="M8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="S8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F9">
-        <v>8000000</v>
+        <v>435000000</v>
       </c>
       <c r="G9">
-        <v>4000000</v>
+        <v>7250000</v>
       </c>
       <c r="H9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I9">
-        <v>2000</v>
+        <v>47000</v>
       </c>
       <c r="J9">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="K9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L9">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="M9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="S9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1273,58 +1255,58 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="F10">
-        <v>28960000</v>
+        <v>8000000</v>
       </c>
       <c r="G10">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I10">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J10">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L10">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="M10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="S10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1335,58 +1317,58 @@
         <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
         <v>26</v>
       </c>
       <c r="F11">
-        <v>57589000</v>
+        <v>28960000</v>
       </c>
       <c r="G11">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I11">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J11">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L11">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="M11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="S11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1397,58 +1379,58 @@
         <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" t="s">
         <v>27</v>
       </c>
-      <c r="E12" t="s">
-        <v>85</v>
-      </c>
       <c r="F12">
-        <v>43200000</v>
+        <v>57589000</v>
       </c>
       <c r="G12">
-        <v>2400000</v>
+        <v>1330000</v>
       </c>
       <c r="H12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I12">
-        <v>11000</v>
+        <v>36400</v>
       </c>
       <c r="J12">
-        <v>14200</v>
+        <v>43300</v>
       </c>
       <c r="K12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L12">
-        <v>18000</v>
+        <v>43300</v>
       </c>
       <c r="M12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="S12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1459,58 +1441,58 @@
         <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F13">
-        <v>23800000</v>
+        <v>43200000</v>
       </c>
       <c r="G13">
-        <v>3400000</v>
+        <v>2400000</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I13">
-        <v>4500</v>
+        <v>11000</v>
       </c>
       <c r="J13">
-        <v>5500</v>
+        <v>14200</v>
       </c>
       <c r="K13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L13">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="M13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="S13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1521,58 +1503,58 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="F14">
-        <v>12500000</v>
+        <v>23800000</v>
       </c>
       <c r="G14">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I14">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J14">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="K14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L14">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="M14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1583,58 +1565,58 @@
         <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F15">
-        <v>23000000</v>
+        <v>12500000</v>
       </c>
       <c r="G15">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I15">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="J15">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="K15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L15">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="M15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1645,58 +1627,58 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
         <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="F16">
-        <v>12900000</v>
+        <v>23000000</v>
       </c>
       <c r="G16">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="H16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I16">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="J16">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="K16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L16">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="M16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="S16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1707,22 +1689,22 @@
         <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="F17">
-        <v>12000000</v>
+        <v>12900000</v>
       </c>
       <c r="G17">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="H17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1731,60 +1713,60 @@
         <v>2000</v>
       </c>
       <c r="K17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L17">
         <v>2000</v>
       </c>
       <c r="M17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R17" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="S17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
         <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="F18">
-        <v>14000000</v>
+        <v>12000000</v>
       </c>
       <c r="G18">
-        <v>7000000</v>
+        <v>6000000</v>
       </c>
       <c r="H18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I18">
         <v>2000</v>
@@ -1793,34 +1775,34 @@
         <v>2000</v>
       </c>
       <c r="K18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L18">
         <v>2000</v>
       </c>
       <c r="M18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R18" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="S18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1831,22 +1813,22 @@
         <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>8000000</v>
+        <v>14000000</v>
       </c>
       <c r="G19">
-        <v>4000000</v>
+        <v>7000000</v>
       </c>
       <c r="H19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I19">
         <v>2000</v>
@@ -1855,282 +1837,96 @@
         <v>2000</v>
       </c>
       <c r="K19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L19">
         <v>2000</v>
       </c>
       <c r="M19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
         <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="F20">
-        <v>9500000</v>
+        <v>70000002</v>
       </c>
       <c r="G20">
-        <v>4750000</v>
+        <v>23333334</v>
       </c>
       <c r="H20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I20">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J20">
-        <v>2000</v>
+        <v>3800</v>
       </c>
       <c r="K20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L20">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="M20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="R20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="S20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21">
-        <v>22100000</v>
-      </c>
-      <c r="G21">
-        <v>1300000</v>
-      </c>
-      <c r="H21" t="s">
-        <v>88</v>
-      </c>
-      <c r="I21">
-        <v>10500</v>
-      </c>
-      <c r="J21">
-        <v>14000</v>
-      </c>
-      <c r="K21" t="s">
-        <v>88</v>
-      </c>
-      <c r="L21">
-        <v>17000</v>
-      </c>
-      <c r="M21" t="s">
-        <v>88</v>
-      </c>
-      <c r="N21" t="s">
-        <v>88</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>88</v>
-      </c>
-      <c r="R21" t="s">
-        <v>108</v>
-      </c>
-      <c r="S21" t="s">
-        <v>88</v>
-      </c>
-      <c r="T21" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22">
-        <v>48000000</v>
-      </c>
-      <c r="G22">
-        <v>1600000</v>
-      </c>
-      <c r="H22" t="s">
-        <v>88</v>
-      </c>
-      <c r="I22">
-        <v>20000</v>
-      </c>
-      <c r="J22">
-        <v>23500</v>
-      </c>
-      <c r="K22" t="s">
-        <v>88</v>
-      </c>
-      <c r="L22">
-        <v>30000</v>
-      </c>
-      <c r="M22" t="s">
-        <v>88</v>
-      </c>
-      <c r="N22" t="s">
-        <v>88</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>88</v>
-      </c>
-      <c r="R22" t="s">
-        <v>109</v>
-      </c>
-      <c r="S22" t="s">
-        <v>88</v>
-      </c>
-      <c r="T22" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23">
-        <v>70000002</v>
-      </c>
-      <c r="G23">
-        <v>23333334</v>
-      </c>
-      <c r="H23" t="s">
-        <v>88</v>
-      </c>
-      <c r="I23">
-        <v>3000</v>
-      </c>
-      <c r="J23">
-        <v>3800</v>
-      </c>
-      <c r="K23" t="s">
-        <v>88</v>
-      </c>
-      <c r="L23">
-        <v>3000</v>
-      </c>
-      <c r="M23" t="s">
-        <v>88</v>
-      </c>
-      <c r="N23" t="s">
-        <v>88</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>88</v>
-      </c>
-      <c r="R23" t="s">
-        <v>110</v>
-      </c>
-      <c r="S23" t="s">
-        <v>88</v>
-      </c>
-      <c r="T23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="102">
   <si>
     <t>청약일</t>
   </si>
@@ -121,7 +121,7 @@
     <t>2024-06-13</t>
   </si>
   <si>
-    <t>2024-06-11</t>
+    <t>교보16호스팩</t>
   </si>
   <si>
     <t>뱅크웨어글로벌</t>
@@ -172,15 +172,12 @@
     <t>미래에셋비전스팩6호</t>
   </si>
   <si>
-    <t>KB제29호스팩</t>
-  </si>
-  <si>
-    <t>에이치엠씨제7호스팩</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
+    <t>교보</t>
+  </si>
+  <si>
     <t>미래</t>
   </si>
   <si>
@@ -208,12 +205,6 @@
     <t>한국</t>
   </si>
   <si>
-    <t>KB</t>
-  </si>
-  <si>
-    <t>현대차</t>
-  </si>
-  <si>
     <t>신한, 한국</t>
   </si>
   <si>
@@ -244,6 +235,9 @@
     <t>2024-06-21</t>
   </si>
   <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
     <t>2024-08-12</t>
   </si>
   <si>
@@ -274,6 +268,9 @@
     <t>-</t>
   </si>
   <si>
+    <t>330.1 : 1</t>
+  </si>
+  <si>
     <t>239.19 : 1</t>
   </si>
   <si>
@@ -320,12 +317,6 @@
   </si>
   <si>
     <t>607 : 1</t>
-  </si>
-  <si>
-    <t>408 : 1</t>
-  </si>
-  <si>
-    <t>205.26 : 1</t>
   </si>
   <si>
     <t>120.3 : 1</t>
@@ -686,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -756,335 +747,335 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F2">
-        <v>22400000</v>
+        <v>11600000</v>
       </c>
       <c r="G2">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I2">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J2">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L2">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="M2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F3">
-        <v>22340000</v>
+        <v>22400000</v>
       </c>
       <c r="G3">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I3">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J3">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L3">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="M3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R3" t="s">
         <v>85</v>
       </c>
-      <c r="Q3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R3" t="s">
-        <v>87</v>
-      </c>
       <c r="S3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F4">
-        <v>29700000</v>
+        <v>22340000</v>
       </c>
       <c r="G4">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I4">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J4">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L4">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="M4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F5">
-        <v>266000000</v>
+        <v>29700000</v>
       </c>
       <c r="G5">
-        <v>7600000</v>
+        <v>1350000</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I5">
-        <v>24000</v>
+        <v>14000</v>
       </c>
       <c r="J5">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="K5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L5">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="M5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O5">
-        <v>14.47368421052632</v>
+        <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="S5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F6">
-        <v>12000000</v>
+        <v>266000000</v>
       </c>
       <c r="G6">
-        <v>6000000</v>
+        <v>7600000</v>
       </c>
       <c r="H6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I6">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J6">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="K6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L6">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="M6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>14.47368421052632</v>
       </c>
       <c r="P6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="F7">
-        <v>8000000</v>
+        <v>12000000</v>
       </c>
       <c r="G7">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I7">
         <v>2000</v>
@@ -1093,158 +1084,158 @@
         <v>2000</v>
       </c>
       <c r="K7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L7">
         <v>2000</v>
       </c>
       <c r="M7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="S7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>16180000</v>
+        <v>8000000</v>
       </c>
       <c r="G8">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I8">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J8">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L8">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="M8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>435000000</v>
+        <v>16180000</v>
       </c>
       <c r="G9">
-        <v>7250000</v>
+        <v>1618000</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I9">
-        <v>47000</v>
+        <v>6200</v>
       </c>
       <c r="J9">
-        <v>60000</v>
+        <v>7700</v>
       </c>
       <c r="K9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L9">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="M9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="S9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1252,521 +1243,521 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F10">
-        <v>8000000</v>
+        <v>435000000</v>
       </c>
       <c r="G10">
-        <v>4000000</v>
+        <v>7250000</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I10">
-        <v>2000</v>
+        <v>47000</v>
       </c>
       <c r="J10">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="K10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L10">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="M10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="F11">
-        <v>28960000</v>
+        <v>8000000</v>
       </c>
       <c r="G11">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I11">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J11">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L11">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="M11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>57589000</v>
+        <v>28960000</v>
       </c>
       <c r="G12">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I12">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J12">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L12">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="M12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F13">
-        <v>43200000</v>
+        <v>57589000</v>
       </c>
       <c r="G13">
-        <v>2400000</v>
+        <v>1330000</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I13">
-        <v>11000</v>
+        <v>36400</v>
       </c>
       <c r="J13">
-        <v>14200</v>
+        <v>43300</v>
       </c>
       <c r="K13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L13">
-        <v>18000</v>
+        <v>43300</v>
       </c>
       <c r="M13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F14">
-        <v>23800000</v>
+        <v>43200000</v>
       </c>
       <c r="G14">
-        <v>3400000</v>
+        <v>2400000</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I14">
-        <v>4500</v>
+        <v>11000</v>
       </c>
       <c r="J14">
-        <v>5500</v>
+        <v>14200</v>
       </c>
       <c r="K14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L14">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="M14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F15">
-        <v>12500000</v>
+        <v>23800000</v>
       </c>
       <c r="G15">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="H15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I15">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J15">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="K15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L15">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="M15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R15" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="S15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F16">
-        <v>23000000</v>
+        <v>12500000</v>
       </c>
       <c r="G16">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="H16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I16">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="J16">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="K16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L16">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="M16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F17">
-        <v>12900000</v>
+        <v>23000000</v>
       </c>
       <c r="G17">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="H17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I17">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="J17">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="K17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L17">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="M17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>12000000</v>
+        <v>12900000</v>
       </c>
       <c r="G18">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="H18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I18">
         <v>2000</v>
@@ -1775,158 +1766,96 @@
         <v>2000</v>
       </c>
       <c r="K18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L18">
         <v>2000</v>
       </c>
       <c r="M18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R18" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="F19">
-        <v>14000000</v>
+        <v>70000002</v>
       </c>
       <c r="G19">
-        <v>7000000</v>
+        <v>23333334</v>
       </c>
       <c r="H19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I19">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J19">
-        <v>2000</v>
+        <v>3800</v>
       </c>
       <c r="K19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L19">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="M19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="T19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20">
-        <v>70000002</v>
-      </c>
-      <c r="G20">
-        <v>23333334</v>
-      </c>
-      <c r="H20" t="s">
-        <v>85</v>
-      </c>
-      <c r="I20">
-        <v>3000</v>
-      </c>
-      <c r="J20">
-        <v>3800</v>
-      </c>
-      <c r="K20" t="s">
-        <v>85</v>
-      </c>
-      <c r="L20">
-        <v>3000</v>
-      </c>
-      <c r="M20" t="s">
-        <v>85</v>
-      </c>
-      <c r="N20" t="s">
-        <v>85</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>85</v>
-      </c>
-      <c r="R20" t="s">
-        <v>104</v>
-      </c>
-      <c r="S20" t="s">
-        <v>85</v>
-      </c>
-      <c r="T20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="103">
   <si>
     <t>청약일</t>
   </si>
@@ -76,6 +76,9 @@
     <t>수수료율</t>
   </si>
   <si>
+    <t>2024-08-09</t>
+  </si>
+  <si>
     <t>2024-08-08</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
     <t>2024-06-19</t>
   </si>
   <si>
+    <t>티디에스팜</t>
+  </si>
+  <si>
     <t>전진건설로봇</t>
   </si>
   <si>
@@ -169,15 +175,15 @@
     <t>에이치브이엠</t>
   </si>
   <si>
+    <t>한국</t>
+  </si>
+  <si>
     <t>미래</t>
   </si>
   <si>
     <t>하나</t>
   </si>
   <si>
-    <t>한국</t>
-  </si>
-  <si>
     <t>키움</t>
   </si>
   <si>
@@ -202,15 +208,15 @@
     <t>엘에스</t>
   </si>
   <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
     <t>2024-08-13</t>
   </si>
   <si>
     <t>2024-08-12</t>
   </si>
   <si>
-    <t>2024-08-09</t>
-  </si>
-  <si>
     <t>2024-07-30</t>
   </si>
   <si>
@@ -232,6 +238,9 @@
     <t>2024-06-25</t>
   </si>
   <si>
+    <t>2024-08-21</t>
+  </si>
+  <si>
     <t>2024-08-19</t>
   </si>
   <si>
@@ -260,6 +269,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>1608.17 : 1</t>
   </si>
   <si>
     <t>1087.3 : 1</t>
@@ -668,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -738,123 +750,123 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2">
-        <v>50781225</v>
+        <v>13000000</v>
       </c>
       <c r="G2">
-        <v>3077650</v>
+        <v>1000000</v>
       </c>
       <c r="H2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I2">
-        <v>13800</v>
+        <v>9500</v>
       </c>
       <c r="J2">
-        <v>15700</v>
+        <v>10700</v>
       </c>
       <c r="K2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L2">
-        <v>16500</v>
+        <v>13000</v>
       </c>
       <c r="M2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="S2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F3">
-        <v>21700000</v>
+        <v>50781225</v>
       </c>
       <c r="G3">
-        <v>1400000</v>
+        <v>3077650</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I3">
-        <v>12500</v>
+        <v>13800</v>
       </c>
       <c r="J3">
-        <v>15500</v>
+        <v>15700</v>
       </c>
       <c r="K3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L3">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="M3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="S3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -862,61 +874,61 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F4">
-        <v>29000000</v>
+        <v>21700000</v>
       </c>
       <c r="G4">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I4">
-        <v>24000</v>
+        <v>12500</v>
       </c>
       <c r="J4">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L4">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="M4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -924,61 +936,61 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5">
-        <v>15771000</v>
+        <v>29000000</v>
       </c>
       <c r="G5">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I5">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J5">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="K5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L5">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="M5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O5">
-        <v>72.87616511318242</v>
+        <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="S5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -986,123 +998,123 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F6">
-        <v>11600000</v>
+        <v>15771000</v>
       </c>
       <c r="G6">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I6">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J6">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L6">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="M6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>72.87616511318242</v>
       </c>
       <c r="P6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="S6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F7">
-        <v>22400000</v>
+        <v>11600000</v>
       </c>
       <c r="G7">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I7">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J7">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L7">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="M7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="S7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1110,61 +1122,61 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="F8">
-        <v>22340000</v>
+        <v>22400000</v>
       </c>
       <c r="G8">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I8">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J8">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L8">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="M8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="S8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1172,61 +1184,61 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>29700000</v>
+        <v>22340000</v>
       </c>
       <c r="G9">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I9">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J9">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L9">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="M9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="S9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1234,61 +1246,61 @@
         <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F10">
-        <v>266000000</v>
+        <v>29700000</v>
       </c>
       <c r="G10">
-        <v>7600000</v>
+        <v>1350000</v>
       </c>
       <c r="H10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I10">
-        <v>24000</v>
+        <v>14000</v>
       </c>
       <c r="J10">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="K10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L10">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="M10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O10">
-        <v>14.47368421052632</v>
+        <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1296,61 +1308,61 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F11">
-        <v>12000000</v>
+        <v>266000000</v>
       </c>
       <c r="G11">
-        <v>6000000</v>
+        <v>7600000</v>
       </c>
       <c r="H11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I11">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J11">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="K11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L11">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="M11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>14.47368421052632</v>
       </c>
       <c r="P11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="S11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1358,25 +1370,25 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="F12">
-        <v>8000000</v>
+        <v>12000000</v>
       </c>
       <c r="G12">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I12">
         <v>2000</v>
@@ -1385,34 +1397,34 @@
         <v>2000</v>
       </c>
       <c r="K12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L12">
         <v>2000</v>
       </c>
       <c r="M12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="S12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1420,61 +1432,61 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>16180000</v>
+        <v>8000000</v>
       </c>
       <c r="G13">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I13">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J13">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L13">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="M13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="S13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1482,123 +1494,123 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="F14">
-        <v>435000000</v>
+        <v>16180000</v>
       </c>
       <c r="G14">
-        <v>7250000</v>
+        <v>1618000</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I14">
-        <v>47000</v>
+        <v>6200</v>
       </c>
       <c r="J14">
-        <v>60000</v>
+        <v>7700</v>
       </c>
       <c r="K14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L14">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="M14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="S14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F15">
-        <v>8000000</v>
+        <v>435000000</v>
       </c>
       <c r="G15">
-        <v>4000000</v>
+        <v>7250000</v>
       </c>
       <c r="H15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I15">
-        <v>2000</v>
+        <v>47000</v>
       </c>
       <c r="J15">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="K15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L15">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="M15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R15" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="S15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1606,61 +1618,61 @@
         <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="F16">
-        <v>28960000</v>
+        <v>8000000</v>
       </c>
       <c r="G16">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I16">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J16">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L16">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="M16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="S16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1668,61 +1680,61 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
       </c>
       <c r="F17">
-        <v>57589000</v>
+        <v>28960000</v>
       </c>
       <c r="G17">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I17">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J17">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L17">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="M17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="S17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1730,61 +1742,123 @@
         <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" t="s">
         <v>31</v>
       </c>
-      <c r="E18" t="s">
-        <v>80</v>
-      </c>
       <c r="F18">
-        <v>43200000</v>
+        <v>57589000</v>
       </c>
       <c r="G18">
-        <v>2400000</v>
+        <v>1330000</v>
       </c>
       <c r="H18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I18">
-        <v>11000</v>
+        <v>36400</v>
       </c>
       <c r="J18">
-        <v>14200</v>
+        <v>43300</v>
       </c>
       <c r="K18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L18">
-        <v>18000</v>
+        <v>43300</v>
       </c>
       <c r="M18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="S18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T18" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19">
+        <v>43200000</v>
+      </c>
+      <c r="G19">
+        <v>2400000</v>
+      </c>
+      <c r="H19" t="s">
+        <v>84</v>
+      </c>
+      <c r="I19">
+        <v>11000</v>
+      </c>
+      <c r="J19">
+        <v>14200</v>
+      </c>
+      <c r="K19" t="s">
+        <v>84</v>
+      </c>
+      <c r="L19">
+        <v>18000</v>
+      </c>
+      <c r="M19" t="s">
+        <v>84</v>
+      </c>
+      <c r="N19" t="s">
+        <v>84</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>84</v>
+      </c>
+      <c r="R19" t="s">
+        <v>102</v>
+      </c>
+      <c r="S19" t="s">
+        <v>84</v>
+      </c>
+      <c r="T19" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="109">
   <si>
     <t>청약일</t>
   </si>
@@ -76,6 +76,9 @@
     <t>수수료율</t>
   </si>
   <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
     <t>2024-08-09</t>
   </si>
   <si>
@@ -121,9 +124,15 @@
     <t>2024-06-19</t>
   </si>
   <si>
+    <t>M83</t>
+  </si>
+  <si>
     <t>티디에스팜</t>
   </si>
   <si>
+    <t>대신밸런스제18호스팩</t>
+  </si>
+  <si>
     <t>전진건설로봇</t>
   </si>
   <si>
@@ -175,9 +184,15 @@
     <t>에이치브이엠</t>
   </si>
   <si>
+    <t>신영</t>
+  </si>
+  <si>
     <t>한국</t>
   </si>
   <si>
+    <t>대신</t>
+  </si>
+  <si>
     <t>미래</t>
   </si>
   <si>
@@ -199,24 +214,21 @@
     <t>SK</t>
   </si>
   <si>
-    <t>대신</t>
-  </si>
-  <si>
     <t>한국, 제이피모간회사 서울지점, NH</t>
   </si>
   <si>
     <t>엘에스</t>
   </si>
   <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
     <t>2024-08-14</t>
   </si>
   <si>
     <t>2024-08-13</t>
   </si>
   <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
     <t>2024-07-30</t>
   </si>
   <si>
@@ -238,6 +250,9 @@
     <t>2024-06-25</t>
   </si>
   <si>
+    <t>2024-08-22</t>
+  </si>
+  <si>
     <t>2024-08-21</t>
   </si>
   <si>
@@ -247,9 +262,6 @@
     <t>2024-08-20</t>
   </si>
   <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
     <t>2024-07-31</t>
   </si>
   <si>
@@ -271,7 +283,13 @@
     <t>-</t>
   </si>
   <si>
+    <t>638.07 : 1</t>
+  </si>
+  <si>
     <t>1608.17 : 1</t>
+  </si>
+  <si>
+    <t>135.53 : 1</t>
   </si>
   <si>
     <t>1087.3 : 1</t>
@@ -680,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -750,61 +768,61 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F2">
-        <v>13000000</v>
+        <v>24000000</v>
       </c>
       <c r="G2">
-        <v>1000000</v>
+        <v>1500000</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I2">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="J2">
-        <v>10700</v>
+        <v>13000</v>
       </c>
       <c r="K2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L2">
-        <v>13000</v>
+        <v>16000</v>
       </c>
       <c r="M2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="S2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -812,61 +830,61 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F3">
-        <v>50781225</v>
+        <v>13000000</v>
       </c>
       <c r="G3">
-        <v>3077650</v>
+        <v>1000000</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I3">
-        <v>13800</v>
+        <v>9500</v>
       </c>
       <c r="J3">
-        <v>15700</v>
+        <v>10700</v>
       </c>
       <c r="K3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L3">
-        <v>16500</v>
+        <v>13000</v>
       </c>
       <c r="M3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="S3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -874,61 +892,61 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F4">
-        <v>21700000</v>
+        <v>13000000</v>
       </c>
       <c r="G4">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I4">
-        <v>12500</v>
+        <v>2000</v>
       </c>
       <c r="J4">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="K4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L4">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="M4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="S4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -936,185 +954,185 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F5">
-        <v>29000000</v>
+        <v>50781225</v>
       </c>
       <c r="G5">
-        <v>1000000</v>
+        <v>3077650</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I5">
-        <v>24000</v>
+        <v>13800</v>
       </c>
       <c r="J5">
-        <v>29000</v>
+        <v>15700</v>
       </c>
       <c r="K5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L5">
-        <v>29000</v>
+        <v>16500</v>
       </c>
       <c r="M5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="S5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F6">
-        <v>15771000</v>
+        <v>21700000</v>
       </c>
       <c r="G6">
-        <v>751000</v>
+        <v>1400000</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I6">
-        <v>18000</v>
+        <v>12500</v>
       </c>
       <c r="J6">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="K6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L6">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="M6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O6">
-        <v>72.87616511318242</v>
+        <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="S6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
         <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F7">
-        <v>11600000</v>
+        <v>29000000</v>
       </c>
       <c r="G7">
-        <v>5800000</v>
+        <v>1000000</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I7">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J7">
-        <v>2000</v>
+        <v>29000</v>
       </c>
       <c r="K7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L7">
-        <v>2000</v>
+        <v>29000</v>
       </c>
       <c r="M7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="S7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1122,61 +1140,61 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F8">
-        <v>22400000</v>
+        <v>15771000</v>
       </c>
       <c r="G8">
-        <v>1400000</v>
+        <v>751000</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I8">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="J8">
-        <v>19000</v>
+        <v>21000</v>
       </c>
       <c r="K8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L8">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="M8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>72.87616511318242</v>
       </c>
       <c r="P8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="S8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1184,433 +1202,433 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="F9">
-        <v>22340000</v>
+        <v>11600000</v>
       </c>
       <c r="G9">
-        <v>2234000</v>
+        <v>5800000</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I9">
-        <v>7300</v>
+        <v>2000</v>
       </c>
       <c r="J9">
-        <v>8500</v>
+        <v>2000</v>
       </c>
       <c r="K9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L9">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="M9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R9" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="S9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>29700000</v>
+        <v>22400000</v>
       </c>
       <c r="G10">
-        <v>1350000</v>
+        <v>1400000</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I10">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="J10">
-        <v>17000</v>
+        <v>19000</v>
       </c>
       <c r="K10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L10">
-        <v>22000</v>
+        <v>16000</v>
       </c>
       <c r="M10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="S10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>266000000</v>
+        <v>22340000</v>
       </c>
       <c r="G11">
-        <v>7600000</v>
+        <v>2234000</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I11">
-        <v>24000</v>
+        <v>7300</v>
       </c>
       <c r="J11">
-        <v>30000</v>
+        <v>8500</v>
       </c>
       <c r="K11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L11">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="M11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O11">
-        <v>14.47368421052632</v>
+        <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="S11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F12">
-        <v>12000000</v>
+        <v>29700000</v>
       </c>
       <c r="G12">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I12">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J12">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L12">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="M12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="S12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="F13">
-        <v>8000000</v>
+        <v>266000000</v>
       </c>
       <c r="G13">
-        <v>4000000</v>
+        <v>7600000</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I13">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J13">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="K13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L13">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="M13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>14.47368421052632</v>
       </c>
       <c r="P13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="S13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="F14">
-        <v>16180000</v>
+        <v>12000000</v>
       </c>
       <c r="G14">
-        <v>1618000</v>
+        <v>6000000</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I14">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J14">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L14">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="M14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="S14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="F15">
-        <v>435000000</v>
+        <v>8000000</v>
       </c>
       <c r="G15">
-        <v>7250000</v>
+        <v>4000000</v>
       </c>
       <c r="H15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I15">
-        <v>47000</v>
+        <v>2000</v>
       </c>
       <c r="J15">
-        <v>60000</v>
+        <v>2000</v>
       </c>
       <c r="K15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L15">
-        <v>60000</v>
+        <v>2000</v>
       </c>
       <c r="M15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="S15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1618,61 +1636,61 @@
         <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="F16">
-        <v>8000000</v>
+        <v>16180000</v>
       </c>
       <c r="G16">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H16" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I16">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J16">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K16" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L16">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="M16" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N16" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q16" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R16" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="S16" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T16" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1680,185 +1698,309 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="F17">
-        <v>28960000</v>
+        <v>435000000</v>
       </c>
       <c r="G17">
-        <v>1810000</v>
+        <v>7250000</v>
       </c>
       <c r="H17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I17">
-        <v>9000</v>
+        <v>47000</v>
       </c>
       <c r="J17">
-        <v>12000</v>
+        <v>60000</v>
       </c>
       <c r="K17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L17">
-        <v>16000</v>
+        <v>60000</v>
       </c>
       <c r="M17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R17" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="S17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="F18">
-        <v>57589000</v>
+        <v>8000000</v>
       </c>
       <c r="G18">
-        <v>1330000</v>
+        <v>4000000</v>
       </c>
       <c r="H18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I18">
-        <v>36400</v>
+        <v>2000</v>
       </c>
       <c r="J18">
-        <v>43300</v>
+        <v>2000</v>
       </c>
       <c r="K18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L18">
-        <v>43300</v>
+        <v>2000</v>
       </c>
       <c r="M18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="S18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="F19">
-        <v>43200000</v>
+        <v>28960000</v>
       </c>
       <c r="G19">
-        <v>2400000</v>
+        <v>1810000</v>
       </c>
       <c r="H19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I19">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="J19">
-        <v>14200</v>
+        <v>12000</v>
       </c>
       <c r="K19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L19">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="M19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R19" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T19" t="s">
-        <v>84</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20">
+        <v>57589000</v>
+      </c>
+      <c r="G20">
+        <v>1330000</v>
+      </c>
+      <c r="H20" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20">
+        <v>36400</v>
+      </c>
+      <c r="J20">
+        <v>43300</v>
+      </c>
+      <c r="K20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L20">
+        <v>43300</v>
+      </c>
+      <c r="M20" t="s">
+        <v>88</v>
+      </c>
+      <c r="N20" t="s">
+        <v>88</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>88</v>
+      </c>
+      <c r="R20" t="s">
+        <v>107</v>
+      </c>
+      <c r="S20" t="s">
+        <v>88</v>
+      </c>
+      <c r="T20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21">
+        <v>43200000</v>
+      </c>
+      <c r="G21">
+        <v>2400000</v>
+      </c>
+      <c r="H21" t="s">
+        <v>88</v>
+      </c>
+      <c r="I21">
+        <v>11000</v>
+      </c>
+      <c r="J21">
+        <v>14200</v>
+      </c>
+      <c r="K21" t="s">
+        <v>88</v>
+      </c>
+      <c r="L21">
+        <v>18000</v>
+      </c>
+      <c r="M21" t="s">
+        <v>88</v>
+      </c>
+      <c r="N21" t="s">
+        <v>88</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>88</v>
+      </c>
+      <c r="R21" t="s">
+        <v>108</v>
+      </c>
+      <c r="S21" t="s">
+        <v>88</v>
+      </c>
+      <c r="T21" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="112">
   <si>
     <t>청약일</t>
   </si>
@@ -127,6 +127,9 @@
     <t>M83</t>
   </si>
   <si>
+    <t>이엔셀</t>
+  </si>
+  <si>
     <t>티디에스팜</t>
   </si>
   <si>
@@ -187,6 +190,9 @@
     <t>신영</t>
   </si>
   <si>
+    <t>NH</t>
+  </si>
+  <si>
     <t>한국</t>
   </si>
   <si>
@@ -208,9 +214,6 @@
     <t>삼성</t>
   </si>
   <si>
-    <t>NH</t>
-  </si>
-  <si>
     <t>SK</t>
   </si>
   <si>
@@ -253,6 +256,9 @@
     <t>2024-08-22</t>
   </si>
   <si>
+    <t>2024-08-23</t>
+  </si>
+  <si>
     <t>2024-08-21</t>
   </si>
   <si>
@@ -284,6 +290,9 @@
   </si>
   <si>
     <t>638.07 : 1</t>
+  </si>
+  <si>
+    <t>928.06 : 1</t>
   </si>
   <si>
     <t>1608.17 : 1</t>
@@ -698,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -771,13 +780,13 @@
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F2">
         <v>24000000</v>
@@ -786,7 +795,7 @@
         <v>1500000</v>
       </c>
       <c r="H2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I2">
         <v>11000</v>
@@ -795,96 +804,96 @@
         <v>13000</v>
       </c>
       <c r="K2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L2">
         <v>16000</v>
       </c>
       <c r="M2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="S2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
         <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
         <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3">
-        <v>13000000</v>
+        <v>23972040</v>
       </c>
       <c r="G3">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="H3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I3">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J3">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L3">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="M3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="S3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -895,120 +904,120 @@
         <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F4">
         <v>13000000</v>
       </c>
       <c r="G4">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="H4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I4">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J4">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L4">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="M4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="S4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
         <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F5">
-        <v>50781225</v>
+        <v>13000000</v>
       </c>
       <c r="G5">
-        <v>3077650</v>
+        <v>6500000</v>
       </c>
       <c r="H5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I5">
-        <v>13800</v>
+        <v>2000</v>
       </c>
       <c r="J5">
-        <v>15700</v>
+        <v>2000</v>
       </c>
       <c r="K5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L5">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="M5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="S5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1019,244 +1028,244 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F6">
-        <v>21700000</v>
+        <v>50781225</v>
       </c>
       <c r="G6">
-        <v>1400000</v>
+        <v>3077650</v>
       </c>
       <c r="H6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I6">
-        <v>12500</v>
+        <v>13800</v>
       </c>
       <c r="J6">
-        <v>15500</v>
+        <v>15700</v>
       </c>
       <c r="K6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L6">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="M6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="S6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F7">
-        <v>29000000</v>
+        <v>21700000</v>
       </c>
       <c r="G7">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="H7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I7">
-        <v>24000</v>
+        <v>12500</v>
       </c>
       <c r="J7">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L7">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="M7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F8">
-        <v>15771000</v>
+        <v>29000000</v>
       </c>
       <c r="G8">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="H8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I8">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J8">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="K8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L8">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="M8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O8">
-        <v>72.87616511318242</v>
+        <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="S8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F9">
-        <v>11600000</v>
+        <v>15771000</v>
       </c>
       <c r="G9">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="H9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I9">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J9">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L9">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="M9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>72.87616511318242</v>
       </c>
       <c r="P9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1267,332 +1276,332 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="F10">
-        <v>22400000</v>
+        <v>11600000</v>
       </c>
       <c r="G10">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I10">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J10">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L10">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="M10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="S10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
         <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>22340000</v>
+        <v>22400000</v>
       </c>
       <c r="G11">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I11">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J11">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L11">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="M11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
         <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>29700000</v>
+        <v>22340000</v>
       </c>
       <c r="G12">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I12">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J12">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L12">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="M12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
         <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F13">
-        <v>266000000</v>
+        <v>29700000</v>
       </c>
       <c r="G13">
-        <v>7600000</v>
+        <v>1350000</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I13">
-        <v>24000</v>
+        <v>14000</v>
       </c>
       <c r="J13">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="K13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L13">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="M13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O13">
-        <v>14.47368421052632</v>
+        <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
         <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F14">
-        <v>12000000</v>
+        <v>266000000</v>
       </c>
       <c r="G14">
-        <v>6000000</v>
+        <v>7600000</v>
       </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I14">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J14">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="K14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L14">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="M14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>14.47368421052632</v>
       </c>
       <c r="P14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="S14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
         <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="F15">
-        <v>8000000</v>
+        <v>12000000</v>
       </c>
       <c r="G15">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I15">
         <v>2000</v>
@@ -1601,158 +1610,158 @@
         <v>2000</v>
       </c>
       <c r="K15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L15">
         <v>2000</v>
       </c>
       <c r="M15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F16">
-        <v>16180000</v>
+        <v>8000000</v>
       </c>
       <c r="G16">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I16">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J16">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L16">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="M16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="S16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
         <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
         <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="F17">
-        <v>435000000</v>
+        <v>16180000</v>
       </c>
       <c r="G17">
-        <v>7250000</v>
+        <v>1618000</v>
       </c>
       <c r="H17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I17">
-        <v>47000</v>
+        <v>6200</v>
       </c>
       <c r="J17">
-        <v>60000</v>
+        <v>7700</v>
       </c>
       <c r="K17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L17">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="M17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1766,241 +1775,303 @@
         <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F18">
-        <v>8000000</v>
+        <v>435000000</v>
       </c>
       <c r="G18">
-        <v>4000000</v>
+        <v>7250000</v>
       </c>
       <c r="H18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I18">
-        <v>2000</v>
+        <v>47000</v>
       </c>
       <c r="J18">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="K18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L18">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="M18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="S18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
         <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
         <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="F19">
-        <v>28960000</v>
+        <v>8000000</v>
       </c>
       <c r="G19">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I19">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J19">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L19">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="M19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="S19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
         <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
         <v>77</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F20">
-        <v>57589000</v>
+        <v>28960000</v>
       </c>
       <c r="G20">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I20">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J20">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L20">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="M20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R20" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="S20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:20">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
         <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>43200000</v>
+        <v>57589000</v>
       </c>
       <c r="G21">
-        <v>2400000</v>
+        <v>1330000</v>
       </c>
       <c r="H21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I21">
-        <v>11000</v>
+        <v>36400</v>
       </c>
       <c r="J21">
-        <v>14200</v>
+        <v>43300</v>
       </c>
       <c r="K21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L21">
-        <v>18000</v>
+        <v>43300</v>
       </c>
       <c r="M21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="S21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T21" t="s">
-        <v>88</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22">
+        <v>43200000</v>
+      </c>
+      <c r="G22">
+        <v>2400000</v>
+      </c>
+      <c r="H22" t="s">
+        <v>90</v>
+      </c>
+      <c r="I22">
+        <v>11000</v>
+      </c>
+      <c r="J22">
+        <v>14200</v>
+      </c>
+      <c r="K22" t="s">
+        <v>90</v>
+      </c>
+      <c r="L22">
+        <v>18000</v>
+      </c>
+      <c r="M22" t="s">
+        <v>90</v>
+      </c>
+      <c r="N22" t="s">
+        <v>90</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>90</v>
+      </c>
+      <c r="R22" t="s">
+        <v>111</v>
+      </c>
+      <c r="S22" t="s">
+        <v>90</v>
+      </c>
+      <c r="T22" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="104">
   <si>
     <t>청약일</t>
   </si>
@@ -118,12 +118,6 @@
     <t>2024-06-24</t>
   </si>
   <si>
-    <t>2024-06-20</t>
-  </si>
-  <si>
-    <t>2024-06-19</t>
-  </si>
-  <si>
     <t>M83</t>
   </si>
   <si>
@@ -181,12 +175,6 @@
     <t>하스</t>
   </si>
   <si>
-    <t>이노스페이스</t>
-  </si>
-  <si>
-    <t>에이치브이엠</t>
-  </si>
-  <si>
     <t>신영</t>
   </si>
   <si>
@@ -250,9 +238,6 @@
     <t>2024-06-27</t>
   </si>
   <si>
-    <t>2024-06-25</t>
-  </si>
-  <si>
     <t>2024-08-22</t>
   </si>
   <si>
@@ -283,9 +268,6 @@
     <t>2024-07-12</t>
   </si>
   <si>
-    <t>2024-06-28</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -344,12 +326,6 @@
   </si>
   <si>
     <t>2126.46 : 1</t>
-  </si>
-  <si>
-    <t>1150.72 : 1</t>
-  </si>
-  <si>
-    <t>960.3509 : 1</t>
   </si>
 </sst>
 </file>
@@ -707,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -777,16 +753,16 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F2">
         <v>24000000</v>
@@ -795,7 +771,7 @@
         <v>1500000</v>
       </c>
       <c r="H2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I2">
         <v>11000</v>
@@ -804,34 +780,34 @@
         <v>13000</v>
       </c>
       <c r="K2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L2">
         <v>16000</v>
       </c>
       <c r="M2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="S2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -839,16 +815,16 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F3">
         <v>23972040</v>
@@ -857,7 +833,7 @@
         <v>1566800</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I3">
         <v>13600</v>
@@ -866,34 +842,34 @@
         <v>15300</v>
       </c>
       <c r="K3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L3">
         <v>15300</v>
       </c>
       <c r="M3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="S3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -901,16 +877,16 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F4">
         <v>13000000</v>
@@ -919,7 +895,7 @@
         <v>1000000</v>
       </c>
       <c r="H4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I4">
         <v>9500</v>
@@ -928,34 +904,34 @@
         <v>10700</v>
       </c>
       <c r="K4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L4">
         <v>13000</v>
       </c>
       <c r="M4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O4">
         <v>50</v>
       </c>
       <c r="P4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="S4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -963,16 +939,16 @@
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F5">
         <v>13000000</v>
@@ -981,7 +957,7 @@
         <v>6500000</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I5">
         <v>2000</v>
@@ -990,34 +966,34 @@
         <v>2000</v>
       </c>
       <c r="K5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L5">
         <v>2000</v>
       </c>
       <c r="M5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="S5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1025,16 +1001,16 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F6">
         <v>50781225</v>
@@ -1043,7 +1019,7 @@
         <v>3077650</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I6">
         <v>13800</v>
@@ -1052,34 +1028,34 @@
         <v>15700</v>
       </c>
       <c r="K6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L6">
         <v>16500</v>
       </c>
       <c r="M6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="S6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1087,16 +1063,16 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F7">
         <v>21700000</v>
@@ -1105,7 +1081,7 @@
         <v>1400000</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I7">
         <v>12500</v>
@@ -1114,34 +1090,34 @@
         <v>15500</v>
       </c>
       <c r="K7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L7">
         <v>15500</v>
       </c>
       <c r="M7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" t="s">
         <v>90</v>
       </c>
-      <c r="Q7" t="s">
-        <v>90</v>
-      </c>
-      <c r="R7" t="s">
-        <v>96</v>
-      </c>
       <c r="S7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1149,16 +1125,16 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F8">
         <v>29000000</v>
@@ -1167,7 +1143,7 @@
         <v>1000000</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I8">
         <v>24000</v>
@@ -1176,34 +1152,34 @@
         <v>29000</v>
       </c>
       <c r="K8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L8">
         <v>29000</v>
       </c>
       <c r="M8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R8" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="S8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1211,16 +1187,16 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F9">
         <v>15771000</v>
@@ -1229,7 +1205,7 @@
         <v>751000</v>
       </c>
       <c r="H9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I9">
         <v>18000</v>
@@ -1238,34 +1214,34 @@
         <v>21000</v>
       </c>
       <c r="K9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L9">
         <v>21000</v>
       </c>
       <c r="M9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O9">
         <v>72.87616511318242</v>
       </c>
       <c r="P9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R9" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="S9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1273,16 +1249,16 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F10">
         <v>11600000</v>
@@ -1291,7 +1267,7 @@
         <v>5800000</v>
       </c>
       <c r="H10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I10">
         <v>2000</v>
@@ -1300,34 +1276,34 @@
         <v>2000</v>
       </c>
       <c r="K10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L10">
         <v>2000</v>
       </c>
       <c r="M10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R10" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="S10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1335,10 +1311,10 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -1353,7 +1329,7 @@
         <v>1400000</v>
       </c>
       <c r="H11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I11">
         <v>16000</v>
@@ -1362,34 +1338,34 @@
         <v>19000</v>
       </c>
       <c r="K11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L11">
         <v>16000</v>
       </c>
       <c r="M11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R11" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="S11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1397,13 +1373,13 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
         <v>24</v>
@@ -1415,7 +1391,7 @@
         <v>2234000</v>
       </c>
       <c r="H12" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I12">
         <v>7300</v>
@@ -1424,34 +1400,34 @@
         <v>8500</v>
       </c>
       <c r="K12" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L12">
         <v>10000</v>
       </c>
       <c r="M12" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N12" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q12" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R12" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="S12" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T12" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1459,16 +1435,16 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F13">
         <v>29700000</v>
@@ -1477,7 +1453,7 @@
         <v>1350000</v>
       </c>
       <c r="H13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I13">
         <v>14000</v>
@@ -1486,34 +1462,34 @@
         <v>17000</v>
       </c>
       <c r="K13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L13">
         <v>22000</v>
       </c>
       <c r="M13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R13" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="S13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1521,16 +1497,16 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F14">
         <v>266000000</v>
@@ -1539,7 +1515,7 @@
         <v>7600000</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I14">
         <v>24000</v>
@@ -1548,34 +1524,34 @@
         <v>30000</v>
       </c>
       <c r="K14" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L14">
         <v>35000</v>
       </c>
       <c r="M14" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N14" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O14">
         <v>14.47368421052632</v>
       </c>
       <c r="P14" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q14" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R14" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S14" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T14" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1583,16 +1559,16 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F15">
         <v>12000000</v>
@@ -1601,7 +1577,7 @@
         <v>6000000</v>
       </c>
       <c r="H15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I15">
         <v>2000</v>
@@ -1610,34 +1586,34 @@
         <v>2000</v>
       </c>
       <c r="K15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L15">
         <v>2000</v>
       </c>
       <c r="M15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R15" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="S15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1645,10 +1621,10 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
@@ -1663,7 +1639,7 @@
         <v>4000000</v>
       </c>
       <c r="H16" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1672,34 +1648,34 @@
         <v>2000</v>
       </c>
       <c r="K16" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L16">
         <v>2000</v>
       </c>
       <c r="M16" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N16" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q16" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R16" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="S16" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T16" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1707,13 +1683,13 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -1725,7 +1701,7 @@
         <v>1618000</v>
       </c>
       <c r="H17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I17">
         <v>6200</v>
@@ -1734,34 +1710,34 @@
         <v>7700</v>
       </c>
       <c r="K17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L17">
         <v>10000</v>
       </c>
       <c r="M17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R17" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="S17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1769,16 +1745,16 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F18">
         <v>435000000</v>
@@ -1787,7 +1763,7 @@
         <v>7250000</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I18">
         <v>47000</v>
@@ -1796,34 +1772,34 @@
         <v>60000</v>
       </c>
       <c r="K18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L18">
         <v>60000</v>
       </c>
       <c r="M18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R18" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="S18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1831,16 +1807,16 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F19">
         <v>8000000</v>
@@ -1849,7 +1825,7 @@
         <v>4000000</v>
       </c>
       <c r="H19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I19">
         <v>2000</v>
@@ -1858,34 +1834,34 @@
         <v>2000</v>
       </c>
       <c r="K19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L19">
         <v>2000</v>
       </c>
       <c r="M19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R19" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="S19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -1893,13 +1869,13 @@
         <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
         <v>31</v>
@@ -1911,7 +1887,7 @@
         <v>1810000</v>
       </c>
       <c r="H20" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I20">
         <v>9000</v>
@@ -1920,158 +1896,34 @@
         <v>12000</v>
       </c>
       <c r="K20" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L20">
         <v>16000</v>
       </c>
       <c r="M20" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N20" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Q20" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="R20" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="S20" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="T20" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21">
-        <v>57589000</v>
-      </c>
-      <c r="G21">
-        <v>1330000</v>
-      </c>
-      <c r="H21" t="s">
-        <v>90</v>
-      </c>
-      <c r="I21">
-        <v>36400</v>
-      </c>
-      <c r="J21">
-        <v>43300</v>
-      </c>
-      <c r="K21" t="s">
-        <v>90</v>
-      </c>
-      <c r="L21">
-        <v>43300</v>
-      </c>
-      <c r="M21" t="s">
-        <v>90</v>
-      </c>
-      <c r="N21" t="s">
-        <v>90</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>90</v>
-      </c>
-      <c r="R21" t="s">
-        <v>110</v>
-      </c>
-      <c r="S21" t="s">
-        <v>90</v>
-      </c>
-      <c r="T21" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22">
-        <v>43200000</v>
-      </c>
-      <c r="G22">
-        <v>2400000</v>
-      </c>
-      <c r="H22" t="s">
-        <v>90</v>
-      </c>
-      <c r="I22">
-        <v>11000</v>
-      </c>
-      <c r="J22">
-        <v>14200</v>
-      </c>
-      <c r="K22" t="s">
-        <v>90</v>
-      </c>
-      <c r="L22">
-        <v>18000</v>
-      </c>
-      <c r="M22" t="s">
-        <v>90</v>
-      </c>
-      <c r="N22" t="s">
-        <v>90</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>90</v>
-      </c>
-      <c r="R22" t="s">
-        <v>111</v>
-      </c>
-      <c r="S22" t="s">
-        <v>90</v>
-      </c>
-      <c r="T22" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="100">
   <si>
     <t>청약일</t>
   </si>
@@ -115,9 +115,6 @@
     <t>2024-07-02</t>
   </si>
   <si>
-    <t>2024-06-24</t>
-  </si>
-  <si>
     <t>M83</t>
   </si>
   <si>
@@ -172,9 +169,6 @@
     <t>이베스트스팩6호</t>
   </si>
   <si>
-    <t>하스</t>
-  </si>
-  <si>
     <t>신영</t>
   </si>
   <si>
@@ -235,9 +229,6 @@
     <t>2024-07-05</t>
   </si>
   <si>
-    <t>2024-06-27</t>
-  </si>
-  <si>
     <t>2024-08-22</t>
   </si>
   <si>
@@ -323,9 +314,6 @@
   </si>
   <si>
     <t>107.32 : 1</t>
-  </si>
-  <si>
-    <t>2126.46 : 1</t>
   </si>
 </sst>
 </file>
@@ -683,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -753,16 +741,16 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F2">
         <v>24000000</v>
@@ -771,7 +759,7 @@
         <v>1500000</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I2">
         <v>11000</v>
@@ -780,34 +768,34 @@
         <v>13000</v>
       </c>
       <c r="K2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L2">
         <v>16000</v>
       </c>
       <c r="M2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="S2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -815,16 +803,16 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F3">
         <v>23972040</v>
@@ -833,7 +821,7 @@
         <v>1566800</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I3">
         <v>13600</v>
@@ -842,34 +830,34 @@
         <v>15300</v>
       </c>
       <c r="K3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L3">
         <v>15300</v>
       </c>
       <c r="M3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="S3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -877,16 +865,16 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F4">
         <v>13000000</v>
@@ -895,7 +883,7 @@
         <v>1000000</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I4">
         <v>9500</v>
@@ -904,34 +892,34 @@
         <v>10700</v>
       </c>
       <c r="K4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L4">
         <v>13000</v>
       </c>
       <c r="M4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O4">
         <v>50</v>
       </c>
       <c r="P4" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>81</v>
+      </c>
+      <c r="R4" t="s">
         <v>84</v>
       </c>
-      <c r="Q4" t="s">
-        <v>84</v>
-      </c>
-      <c r="R4" t="s">
-        <v>87</v>
-      </c>
       <c r="S4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -939,16 +927,16 @@
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F5">
         <v>13000000</v>
@@ -957,7 +945,7 @@
         <v>6500000</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I5">
         <v>2000</v>
@@ -966,34 +954,34 @@
         <v>2000</v>
       </c>
       <c r="K5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L5">
         <v>2000</v>
       </c>
       <c r="M5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1001,16 +989,16 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F6">
         <v>50781225</v>
@@ -1019,7 +1007,7 @@
         <v>3077650</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I6">
         <v>13800</v>
@@ -1028,34 +1016,34 @@
         <v>15700</v>
       </c>
       <c r="K6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L6">
         <v>16500</v>
       </c>
       <c r="M6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1063,16 +1051,16 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F7">
         <v>21700000</v>
@@ -1081,7 +1069,7 @@
         <v>1400000</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I7">
         <v>12500</v>
@@ -1090,34 +1078,34 @@
         <v>15500</v>
       </c>
       <c r="K7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L7">
         <v>15500</v>
       </c>
       <c r="M7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1125,16 +1113,16 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F8">
         <v>29000000</v>
@@ -1143,7 +1131,7 @@
         <v>1000000</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I8">
         <v>24000</v>
@@ -1152,34 +1140,34 @@
         <v>29000</v>
       </c>
       <c r="K8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L8">
         <v>29000</v>
       </c>
       <c r="M8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="S8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1187,16 +1175,16 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F9">
         <v>15771000</v>
@@ -1205,7 +1193,7 @@
         <v>751000</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I9">
         <v>18000</v>
@@ -1214,34 +1202,34 @@
         <v>21000</v>
       </c>
       <c r="K9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L9">
         <v>21000</v>
       </c>
       <c r="M9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O9">
         <v>72.87616511318242</v>
       </c>
       <c r="P9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="S9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1249,16 +1237,16 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F10">
         <v>11600000</v>
@@ -1267,7 +1255,7 @@
         <v>5800000</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I10">
         <v>2000</v>
@@ -1276,34 +1264,34 @@
         <v>2000</v>
       </c>
       <c r="K10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L10">
         <v>2000</v>
       </c>
       <c r="M10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="S10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1311,10 +1299,10 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -1329,7 +1317,7 @@
         <v>1400000</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I11">
         <v>16000</v>
@@ -1338,34 +1326,34 @@
         <v>19000</v>
       </c>
       <c r="K11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L11">
         <v>16000</v>
       </c>
       <c r="M11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="S11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1373,13 +1361,13 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>24</v>
@@ -1391,7 +1379,7 @@
         <v>2234000</v>
       </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I12">
         <v>7300</v>
@@ -1400,34 +1388,34 @@
         <v>8500</v>
       </c>
       <c r="K12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L12">
         <v>10000</v>
       </c>
       <c r="M12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="S12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1435,16 +1423,16 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F13">
         <v>29700000</v>
@@ -1453,7 +1441,7 @@
         <v>1350000</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I13">
         <v>14000</v>
@@ -1462,34 +1450,34 @@
         <v>17000</v>
       </c>
       <c r="K13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L13">
         <v>22000</v>
       </c>
       <c r="M13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="S13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1497,16 +1485,16 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F14">
         <v>266000000</v>
@@ -1515,7 +1503,7 @@
         <v>7600000</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I14">
         <v>24000</v>
@@ -1524,34 +1512,34 @@
         <v>30000</v>
       </c>
       <c r="K14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L14">
         <v>35000</v>
       </c>
       <c r="M14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O14">
         <v>14.47368421052632</v>
       </c>
       <c r="P14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="S14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1559,16 +1547,16 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F15">
         <v>12000000</v>
@@ -1577,7 +1565,7 @@
         <v>6000000</v>
       </c>
       <c r="H15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I15">
         <v>2000</v>
@@ -1586,34 +1574,34 @@
         <v>2000</v>
       </c>
       <c r="K15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L15">
         <v>2000</v>
       </c>
       <c r="M15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="S15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1621,10 +1609,10 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
@@ -1639,7 +1627,7 @@
         <v>4000000</v>
       </c>
       <c r="H16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1648,34 +1636,34 @@
         <v>2000</v>
       </c>
       <c r="K16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L16">
         <v>2000</v>
       </c>
       <c r="M16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R16" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="S16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1683,13 +1671,13 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -1701,7 +1689,7 @@
         <v>1618000</v>
       </c>
       <c r="H17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I17">
         <v>6200</v>
@@ -1710,34 +1698,34 @@
         <v>7700</v>
       </c>
       <c r="K17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L17">
         <v>10000</v>
       </c>
       <c r="M17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="S17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1745,16 +1733,16 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F18">
         <v>435000000</v>
@@ -1763,7 +1751,7 @@
         <v>7250000</v>
       </c>
       <c r="H18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I18">
         <v>47000</v>
@@ -1772,34 +1760,34 @@
         <v>60000</v>
       </c>
       <c r="K18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L18">
         <v>60000</v>
       </c>
       <c r="M18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R18" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1807,16 +1795,16 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F19">
         <v>8000000</v>
@@ -1825,7 +1813,7 @@
         <v>4000000</v>
       </c>
       <c r="H19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I19">
         <v>2000</v>
@@ -1834,96 +1822,34 @@
         <v>2000</v>
       </c>
       <c r="K19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L19">
         <v>2000</v>
       </c>
       <c r="M19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R19" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20">
-        <v>28960000</v>
-      </c>
-      <c r="G20">
-        <v>1810000</v>
-      </c>
-      <c r="H20" t="s">
-        <v>84</v>
-      </c>
-      <c r="I20">
-        <v>9000</v>
-      </c>
-      <c r="J20">
-        <v>12000</v>
-      </c>
-      <c r="K20" t="s">
-        <v>84</v>
-      </c>
-      <c r="L20">
-        <v>16000</v>
-      </c>
-      <c r="M20" t="s">
-        <v>84</v>
-      </c>
-      <c r="N20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>84</v>
-      </c>
-      <c r="R20" t="s">
-        <v>103</v>
-      </c>
-      <c r="S20" t="s">
-        <v>84</v>
-      </c>
-      <c r="T20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="104">
   <si>
     <t>청약일</t>
   </si>
@@ -76,6 +76,9 @@
     <t>수수료율</t>
   </si>
   <si>
+    <t>2024-08-21</t>
+  </si>
+  <si>
     <t>2024-08-12</t>
   </si>
   <si>
@@ -115,6 +118,9 @@
     <t>2024-07-02</t>
   </si>
   <si>
+    <t>아이스크림미디어</t>
+  </si>
+  <si>
     <t>M83</t>
   </si>
   <si>
@@ -169,6 +175,9 @@
     <t>이베스트스팩6호</t>
   </si>
   <si>
+    <t>삼성</t>
+  </si>
+  <si>
     <t>신영</t>
   </si>
   <si>
@@ -193,9 +202,6 @@
     <t>교보</t>
   </si>
   <si>
-    <t>삼성</t>
-  </si>
-  <si>
     <t>SK</t>
   </si>
   <si>
@@ -205,6 +211,9 @@
     <t>엘에스</t>
   </si>
   <si>
+    <t>2024-08-26</t>
+  </si>
+  <si>
     <t>2024-08-16</t>
   </si>
   <si>
@@ -229,15 +238,15 @@
     <t>2024-07-05</t>
   </si>
   <si>
+    <t>2024-08-30</t>
+  </si>
+  <si>
     <t>2024-08-22</t>
   </si>
   <si>
     <t>2024-08-23</t>
   </si>
   <si>
-    <t>2024-08-21</t>
-  </si>
-  <si>
     <t>2024-08-19</t>
   </si>
   <si>
@@ -260,6 +269,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>12.89 : 1</t>
   </si>
   <si>
     <t>638.07 : 1</t>
@@ -671,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -741,123 +753,123 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F2">
-        <v>24000000</v>
+        <v>78720000</v>
       </c>
       <c r="G2">
-        <v>1500000</v>
+        <v>2460000</v>
       </c>
       <c r="H2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I2">
-        <v>11000</v>
+        <v>32000</v>
       </c>
       <c r="J2">
-        <v>13000</v>
+        <v>40200</v>
       </c>
       <c r="K2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L2">
-        <v>16000</v>
+        <v>32000</v>
       </c>
       <c r="M2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="S2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F3">
-        <v>23972040</v>
+        <v>24000000</v>
       </c>
       <c r="G3">
-        <v>1566800</v>
+        <v>1500000</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I3">
-        <v>13600</v>
+        <v>11000</v>
       </c>
       <c r="J3">
-        <v>15300</v>
+        <v>13000</v>
       </c>
       <c r="K3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L3">
-        <v>15300</v>
+        <v>16000</v>
       </c>
       <c r="M3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="S3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -865,123 +877,123 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F4">
-        <v>13000000</v>
+        <v>23972040</v>
       </c>
       <c r="G4">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I4">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J4">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L4">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="M4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>13000000</v>
       </c>
       <c r="G5">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I5">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J5">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L5">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="M5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="S5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -989,123 +1001,123 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F6">
-        <v>50781225</v>
+        <v>13000000</v>
       </c>
       <c r="G6">
-        <v>3077650</v>
+        <v>6500000</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I6">
-        <v>13800</v>
+        <v>2000</v>
       </c>
       <c r="J6">
-        <v>15700</v>
+        <v>2000</v>
       </c>
       <c r="K6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L6">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="M6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="S6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F7">
-        <v>21700000</v>
+        <v>50781225</v>
       </c>
       <c r="G7">
-        <v>1400000</v>
+        <v>3077650</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I7">
-        <v>12500</v>
+        <v>13800</v>
       </c>
       <c r="J7">
-        <v>15500</v>
+        <v>15700</v>
       </c>
       <c r="K7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L7">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="M7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="S7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1113,61 +1125,61 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F8">
-        <v>29000000</v>
+        <v>21700000</v>
       </c>
       <c r="G8">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="H8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I8">
-        <v>24000</v>
+        <v>12500</v>
       </c>
       <c r="J8">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L8">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="M8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="S8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1175,61 +1187,61 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="F9">
-        <v>15771000</v>
+        <v>29000000</v>
       </c>
       <c r="G9">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="H9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I9">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J9">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="K9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L9">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="M9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O9">
-        <v>72.87616511318242</v>
+        <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="S9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1237,123 +1249,123 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F10">
-        <v>11600000</v>
+        <v>15771000</v>
       </c>
       <c r="G10">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="H10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I10">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J10">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L10">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="M10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>72.87616511318242</v>
       </c>
       <c r="P10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
         <v>25</v>
       </c>
-      <c r="B11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="F11">
-        <v>22400000</v>
+        <v>11600000</v>
       </c>
       <c r="G11">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I11">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J11">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L11">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="M11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="S11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1361,61 +1373,61 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F12">
-        <v>22340000</v>
+        <v>22400000</v>
       </c>
       <c r="G12">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I12">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J12">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L12">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="M12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="S12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1423,61 +1435,61 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>29700000</v>
+        <v>22340000</v>
       </c>
       <c r="G13">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I13">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J13">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L13">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="M13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="S13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1485,61 +1497,61 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F14">
-        <v>266000000</v>
+        <v>29700000</v>
       </c>
       <c r="G14">
-        <v>7600000</v>
+        <v>1350000</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I14">
-        <v>24000</v>
+        <v>14000</v>
       </c>
       <c r="J14">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="K14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L14">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="M14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O14">
-        <v>14.47368421052632</v>
+        <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="S14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1547,61 +1559,61 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F15">
-        <v>12000000</v>
+        <v>266000000</v>
       </c>
       <c r="G15">
-        <v>6000000</v>
+        <v>7600000</v>
       </c>
       <c r="H15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I15">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J15">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="K15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L15">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="M15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>14.47368421052632</v>
       </c>
       <c r="P15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R15" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="S15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1609,25 +1621,25 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="F16">
-        <v>8000000</v>
+        <v>12000000</v>
       </c>
       <c r="G16">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1636,34 +1648,34 @@
         <v>2000</v>
       </c>
       <c r="K16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L16">
         <v>2000</v>
       </c>
       <c r="M16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="S16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1671,61 +1683,61 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>16180000</v>
+        <v>8000000</v>
       </c>
       <c r="G17">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I17">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J17">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L17">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="M17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="S17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1733,123 +1745,185 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>435000000</v>
+        <v>16180000</v>
       </c>
       <c r="G18">
-        <v>7250000</v>
+        <v>1618000</v>
       </c>
       <c r="H18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I18">
-        <v>47000</v>
+        <v>6200</v>
       </c>
       <c r="J18">
-        <v>60000</v>
+        <v>7700</v>
       </c>
       <c r="K18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L18">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="M18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="S18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F19">
-        <v>8000000</v>
+        <v>435000000</v>
       </c>
       <c r="G19">
-        <v>4000000</v>
+        <v>7250000</v>
       </c>
       <c r="H19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I19">
-        <v>2000</v>
+        <v>47000</v>
       </c>
       <c r="J19">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="K19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L19">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="M19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="S19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="T19" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20">
+        <v>8000000</v>
+      </c>
+      <c r="G20">
+        <v>4000000</v>
+      </c>
+      <c r="H20" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20">
+        <v>2000</v>
+      </c>
+      <c r="J20">
+        <v>2000</v>
+      </c>
+      <c r="K20" t="s">
+        <v>84</v>
+      </c>
+      <c r="L20">
+        <v>2000</v>
+      </c>
+      <c r="M20" t="s">
+        <v>84</v>
+      </c>
+      <c r="N20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>84</v>
+      </c>
+      <c r="R20" t="s">
+        <v>103</v>
+      </c>
+      <c r="S20" t="s">
+        <v>84</v>
+      </c>
+      <c r="T20" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="94">
   <si>
     <t>청약일</t>
   </si>
@@ -115,9 +115,6 @@
     <t>2024-07-03</t>
   </si>
   <si>
-    <t>2024-07-02</t>
-  </si>
-  <si>
     <t>아이스크림미디어</t>
   </si>
   <si>
@@ -169,12 +166,6 @@
     <t>엑셀세라퓨틱스</t>
   </si>
   <si>
-    <t>시프트업</t>
-  </si>
-  <si>
-    <t>이베스트스팩6호</t>
-  </si>
-  <si>
     <t>삼성</t>
   </si>
   <si>
@@ -205,12 +196,6 @@
     <t>SK</t>
   </si>
   <si>
-    <t>한국, 제이피모간회사 서울지점, NH</t>
-  </si>
-  <si>
-    <t>엘에스</t>
-  </si>
-  <si>
     <t>2024-08-26</t>
   </si>
   <si>
@@ -235,9 +220,6 @@
     <t>2024-07-08</t>
   </si>
   <si>
-    <t>2024-07-05</t>
-  </si>
-  <si>
     <t>2024-08-30</t>
   </si>
   <si>
@@ -262,12 +244,6 @@
     <t>2024-07-26</t>
   </si>
   <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -320,12 +296,6 @@
   </si>
   <si>
     <t>517.7 : 1</t>
-  </si>
-  <si>
-    <t>341.24 : 1</t>
-  </si>
-  <si>
-    <t>107.32 : 1</t>
   </si>
 </sst>
 </file>
@@ -683,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -753,16 +723,16 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F2">
         <v>78720000</v>
@@ -771,7 +741,7 @@
         <v>2460000</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I2">
         <v>32000</v>
@@ -780,34 +750,34 @@
         <v>40200</v>
       </c>
       <c r="K2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L2">
         <v>32000</v>
       </c>
       <c r="M2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="S2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -815,16 +785,16 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F3">
         <v>24000000</v>
@@ -833,7 +803,7 @@
         <v>1500000</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I3">
         <v>11000</v>
@@ -842,34 +812,34 @@
         <v>13000</v>
       </c>
       <c r="K3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L3">
         <v>16000</v>
       </c>
       <c r="M3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="S3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -877,16 +847,16 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F4">
         <v>23972040</v>
@@ -895,7 +865,7 @@
         <v>1566800</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I4">
         <v>13600</v>
@@ -904,34 +874,34 @@
         <v>15300</v>
       </c>
       <c r="K4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L4">
         <v>15300</v>
       </c>
       <c r="M4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="S4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -939,13 +909,13 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -957,7 +927,7 @@
         <v>1000000</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I5">
         <v>9500</v>
@@ -966,34 +936,34 @@
         <v>10700</v>
       </c>
       <c r="K5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L5">
         <v>13000</v>
       </c>
       <c r="M5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O5">
         <v>50</v>
       </c>
       <c r="P5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="S5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1001,16 +971,16 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F6">
         <v>13000000</v>
@@ -1019,7 +989,7 @@
         <v>6500000</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I6">
         <v>2000</v>
@@ -1028,34 +998,34 @@
         <v>2000</v>
       </c>
       <c r="K6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L6">
         <v>2000</v>
       </c>
       <c r="M6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R6" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="S6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1063,16 +1033,16 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F7">
         <v>50781225</v>
@@ -1081,7 +1051,7 @@
         <v>3077650</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I7">
         <v>13800</v>
@@ -1090,34 +1060,34 @@
         <v>15700</v>
       </c>
       <c r="K7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L7">
         <v>16500</v>
       </c>
       <c r="M7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="S7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1125,16 +1095,16 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F8">
         <v>21700000</v>
@@ -1143,7 +1113,7 @@
         <v>1400000</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I8">
         <v>12500</v>
@@ -1152,34 +1122,34 @@
         <v>15500</v>
       </c>
       <c r="K8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L8">
         <v>15500</v>
       </c>
       <c r="M8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R8" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="S8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1187,16 +1157,16 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F9">
         <v>29000000</v>
@@ -1205,7 +1175,7 @@
         <v>1000000</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I9">
         <v>24000</v>
@@ -1214,34 +1184,34 @@
         <v>29000</v>
       </c>
       <c r="K9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L9">
         <v>29000</v>
       </c>
       <c r="M9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>76</v>
+      </c>
+      <c r="R9" t="s">
         <v>84</v>
       </c>
-      <c r="Q9" t="s">
-        <v>84</v>
-      </c>
-      <c r="R9" t="s">
-        <v>92</v>
-      </c>
       <c r="S9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1249,16 +1219,16 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F10">
         <v>15771000</v>
@@ -1267,7 +1237,7 @@
         <v>751000</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I10">
         <v>18000</v>
@@ -1276,34 +1246,34 @@
         <v>21000</v>
       </c>
       <c r="K10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L10">
         <v>21000</v>
       </c>
       <c r="M10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O10">
         <v>72.87616511318242</v>
       </c>
       <c r="P10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R10" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="S10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1311,16 +1281,16 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F11">
         <v>11600000</v>
@@ -1329,7 +1299,7 @@
         <v>5800000</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I11">
         <v>2000</v>
@@ -1338,34 +1308,34 @@
         <v>2000</v>
       </c>
       <c r="K11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L11">
         <v>2000</v>
       </c>
       <c r="M11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="S11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1373,10 +1343,10 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -1391,7 +1361,7 @@
         <v>1400000</v>
       </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I12">
         <v>16000</v>
@@ -1400,34 +1370,34 @@
         <v>19000</v>
       </c>
       <c r="K12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L12">
         <v>16000</v>
       </c>
       <c r="M12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R12" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="S12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1435,13 +1405,13 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>25</v>
@@ -1453,7 +1423,7 @@
         <v>2234000</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I13">
         <v>7300</v>
@@ -1462,34 +1432,34 @@
         <v>8500</v>
       </c>
       <c r="K13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L13">
         <v>10000</v>
       </c>
       <c r="M13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R13" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="S13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1497,16 +1467,16 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F14">
         <v>29700000</v>
@@ -1515,7 +1485,7 @@
         <v>1350000</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I14">
         <v>14000</v>
@@ -1524,34 +1494,34 @@
         <v>17000</v>
       </c>
       <c r="K14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L14">
         <v>22000</v>
       </c>
       <c r="M14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="S14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1559,16 +1529,16 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F15">
         <v>266000000</v>
@@ -1577,7 +1547,7 @@
         <v>7600000</v>
       </c>
       <c r="H15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I15">
         <v>24000</v>
@@ -1586,34 +1556,34 @@
         <v>30000</v>
       </c>
       <c r="K15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L15">
         <v>35000</v>
       </c>
       <c r="M15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O15">
         <v>14.47368421052632</v>
       </c>
       <c r="P15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R15" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="S15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1621,16 +1591,16 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F16">
         <v>12000000</v>
@@ -1639,7 +1609,7 @@
         <v>6000000</v>
       </c>
       <c r="H16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1648,34 +1618,34 @@
         <v>2000</v>
       </c>
       <c r="K16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L16">
         <v>2000</v>
       </c>
       <c r="M16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R16" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="S16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1683,10 +1653,10 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
         <v>29</v>
@@ -1701,7 +1671,7 @@
         <v>4000000</v>
       </c>
       <c r="H17" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1710,34 +1680,34 @@
         <v>2000</v>
       </c>
       <c r="K17" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L17">
         <v>2000</v>
       </c>
       <c r="M17" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N17" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q17" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R17" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="S17" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T17" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1745,13 +1715,13 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
         <v>31</v>
@@ -1763,7 +1733,7 @@
         <v>1618000</v>
       </c>
       <c r="H18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I18">
         <v>6200</v>
@@ -1772,158 +1742,34 @@
         <v>7700</v>
       </c>
       <c r="K18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L18">
         <v>10000</v>
       </c>
       <c r="M18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R18" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="S18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="T18" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" t="s">
-        <v>82</v>
-      </c>
-      <c r="F19">
-        <v>435000000</v>
-      </c>
-      <c r="G19">
-        <v>7250000</v>
-      </c>
-      <c r="H19" t="s">
-        <v>84</v>
-      </c>
-      <c r="I19">
-        <v>47000</v>
-      </c>
-      <c r="J19">
-        <v>60000</v>
-      </c>
-      <c r="K19" t="s">
-        <v>84</v>
-      </c>
-      <c r="L19">
-        <v>60000</v>
-      </c>
-      <c r="M19" t="s">
-        <v>84</v>
-      </c>
-      <c r="N19" t="s">
-        <v>84</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>84</v>
-      </c>
-      <c r="R19" t="s">
-        <v>102</v>
-      </c>
-      <c r="S19" t="s">
-        <v>84</v>
-      </c>
-      <c r="T19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" t="s">
-        <v>83</v>
-      </c>
-      <c r="F20">
-        <v>8000000</v>
-      </c>
-      <c r="G20">
-        <v>4000000</v>
-      </c>
-      <c r="H20" t="s">
-        <v>84</v>
-      </c>
-      <c r="I20">
-        <v>2000</v>
-      </c>
-      <c r="J20">
-        <v>2000</v>
-      </c>
-      <c r="K20" t="s">
-        <v>84</v>
-      </c>
-      <c r="L20">
-        <v>2000</v>
-      </c>
-      <c r="M20" t="s">
-        <v>84</v>
-      </c>
-      <c r="N20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>84</v>
-      </c>
-      <c r="R20" t="s">
-        <v>103</v>
-      </c>
-      <c r="S20" t="s">
-        <v>84</v>
-      </c>
-      <c r="T20" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="90">
   <si>
     <t>청약일</t>
   </si>
@@ -112,9 +112,6 @@
     <t>2024-07-15</t>
   </si>
   <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
     <t>아이스크림미디어</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
     <t>SK증권제13호스팩</t>
   </si>
   <si>
-    <t>엑셀세라퓨틱스</t>
-  </si>
-  <si>
     <t>삼성</t>
   </si>
   <si>
@@ -217,9 +211,6 @@
     <t>2024-07-19</t>
   </si>
   <si>
-    <t>2024-07-08</t>
-  </si>
-  <si>
     <t>2024-08-30</t>
   </si>
   <si>
@@ -293,9 +284,6 @@
   </si>
   <si>
     <t>1654.28 : 1</t>
-  </si>
-  <si>
-    <t>517.7 : 1</t>
   </si>
 </sst>
 </file>
@@ -653,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -723,16 +711,16 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F2">
         <v>78720000</v>
@@ -741,7 +729,7 @@
         <v>2460000</v>
       </c>
       <c r="H2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I2">
         <v>32000</v>
@@ -750,34 +738,34 @@
         <v>40200</v>
       </c>
       <c r="K2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L2">
         <v>32000</v>
       </c>
       <c r="M2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="S2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -785,16 +773,16 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F3">
         <v>24000000</v>
@@ -803,7 +791,7 @@
         <v>1500000</v>
       </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I3">
         <v>11000</v>
@@ -812,34 +800,34 @@
         <v>13000</v>
       </c>
       <c r="K3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L3">
         <v>16000</v>
       </c>
       <c r="M3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="S3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -847,16 +835,16 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F4">
         <v>23972040</v>
@@ -865,7 +853,7 @@
         <v>1566800</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I4">
         <v>13600</v>
@@ -874,34 +862,34 @@
         <v>15300</v>
       </c>
       <c r="K4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L4">
         <v>15300</v>
       </c>
       <c r="M4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>73</v>
+      </c>
+      <c r="R4" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" t="s">
-        <v>76</v>
-      </c>
-      <c r="R4" t="s">
-        <v>79</v>
-      </c>
       <c r="S4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -909,13 +897,13 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -927,7 +915,7 @@
         <v>1000000</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I5">
         <v>9500</v>
@@ -936,34 +924,34 @@
         <v>10700</v>
       </c>
       <c r="K5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L5">
         <v>13000</v>
       </c>
       <c r="M5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O5">
         <v>50</v>
       </c>
       <c r="P5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="S5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -971,16 +959,16 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F6">
         <v>13000000</v>
@@ -989,7 +977,7 @@
         <v>6500000</v>
       </c>
       <c r="H6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I6">
         <v>2000</v>
@@ -998,34 +986,34 @@
         <v>2000</v>
       </c>
       <c r="K6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L6">
         <v>2000</v>
       </c>
       <c r="M6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="S6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1033,16 +1021,16 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F7">
         <v>50781225</v>
@@ -1051,7 +1039,7 @@
         <v>3077650</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I7">
         <v>13800</v>
@@ -1060,34 +1048,34 @@
         <v>15700</v>
       </c>
       <c r="K7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L7">
         <v>16500</v>
       </c>
       <c r="M7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="S7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1095,16 +1083,16 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F8">
         <v>21700000</v>
@@ -1113,7 +1101,7 @@
         <v>1400000</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I8">
         <v>12500</v>
@@ -1122,34 +1110,34 @@
         <v>15500</v>
       </c>
       <c r="K8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L8">
         <v>15500</v>
       </c>
       <c r="M8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="S8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1157,16 +1145,16 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F9">
         <v>29000000</v>
@@ -1175,7 +1163,7 @@
         <v>1000000</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I9">
         <v>24000</v>
@@ -1184,34 +1172,34 @@
         <v>29000</v>
       </c>
       <c r="K9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L9">
         <v>29000</v>
       </c>
       <c r="M9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="S9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1219,16 +1207,16 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F10">
         <v>15771000</v>
@@ -1237,7 +1225,7 @@
         <v>751000</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I10">
         <v>18000</v>
@@ -1246,34 +1234,34 @@
         <v>21000</v>
       </c>
       <c r="K10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L10">
         <v>21000</v>
       </c>
       <c r="M10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O10">
         <v>72.87616511318242</v>
       </c>
       <c r="P10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="S10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1281,16 +1269,16 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F11">
         <v>11600000</v>
@@ -1299,7 +1287,7 @@
         <v>5800000</v>
       </c>
       <c r="H11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I11">
         <v>2000</v>
@@ -1308,34 +1296,34 @@
         <v>2000</v>
       </c>
       <c r="K11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L11">
         <v>2000</v>
       </c>
       <c r="M11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="S11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1343,10 +1331,10 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -1361,7 +1349,7 @@
         <v>1400000</v>
       </c>
       <c r="H12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I12">
         <v>16000</v>
@@ -1370,34 +1358,34 @@
         <v>19000</v>
       </c>
       <c r="K12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L12">
         <v>16000</v>
       </c>
       <c r="M12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1405,13 +1393,13 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>25</v>
@@ -1423,7 +1411,7 @@
         <v>2234000</v>
       </c>
       <c r="H13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I13">
         <v>7300</v>
@@ -1432,34 +1420,34 @@
         <v>8500</v>
       </c>
       <c r="K13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L13">
         <v>10000</v>
       </c>
       <c r="M13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1467,16 +1455,16 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F14">
         <v>29700000</v>
@@ -1485,7 +1473,7 @@
         <v>1350000</v>
       </c>
       <c r="H14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I14">
         <v>14000</v>
@@ -1494,34 +1482,34 @@
         <v>17000</v>
       </c>
       <c r="K14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L14">
         <v>22000</v>
       </c>
       <c r="M14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1529,16 +1517,16 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F15">
         <v>266000000</v>
@@ -1547,7 +1535,7 @@
         <v>7600000</v>
       </c>
       <c r="H15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I15">
         <v>24000</v>
@@ -1556,34 +1544,34 @@
         <v>30000</v>
       </c>
       <c r="K15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L15">
         <v>35000</v>
       </c>
       <c r="M15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O15">
         <v>14.47368421052632</v>
       </c>
       <c r="P15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1591,16 +1579,16 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F16">
         <v>12000000</v>
@@ -1609,7 +1597,7 @@
         <v>6000000</v>
       </c>
       <c r="H16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1618,34 +1606,34 @@
         <v>2000</v>
       </c>
       <c r="K16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L16">
         <v>2000</v>
       </c>
       <c r="M16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="S16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1653,10 +1641,10 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
         <v>29</v>
@@ -1671,7 +1659,7 @@
         <v>4000000</v>
       </c>
       <c r="H17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1680,96 +1668,34 @@
         <v>2000</v>
       </c>
       <c r="K17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L17">
         <v>2000</v>
       </c>
       <c r="M17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="S17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="T17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18">
-        <v>16180000</v>
-      </c>
-      <c r="G18">
-        <v>1618000</v>
-      </c>
-      <c r="H18" t="s">
-        <v>76</v>
-      </c>
-      <c r="I18">
-        <v>6200</v>
-      </c>
-      <c r="J18">
-        <v>7700</v>
-      </c>
-      <c r="K18" t="s">
-        <v>76</v>
-      </c>
-      <c r="L18">
-        <v>10000</v>
-      </c>
-      <c r="M18" t="s">
-        <v>76</v>
-      </c>
-      <c r="N18" t="s">
-        <v>76</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>76</v>
-      </c>
-      <c r="R18" t="s">
-        <v>93</v>
-      </c>
-      <c r="S18" t="s">
-        <v>76</v>
-      </c>
-      <c r="T18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="95">
   <si>
     <t>청약일</t>
   </si>
@@ -76,6 +76,9 @@
     <t>수수료율</t>
   </si>
   <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
     <t>2024-08-21</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>2024-07-15</t>
   </si>
   <si>
+    <t>미래에셋비전스팩7호</t>
+  </si>
+  <si>
     <t>아이스크림미디어</t>
   </si>
   <si>
@@ -160,6 +166,9 @@
     <t>SK증권제13호스팩</t>
   </si>
   <si>
+    <t>미래</t>
+  </si>
+  <si>
     <t>삼성</t>
   </si>
   <si>
@@ -175,9 +184,6 @@
     <t>대신</t>
   </si>
   <si>
-    <t>미래</t>
-  </si>
-  <si>
     <t>하나</t>
   </si>
   <si>
@@ -190,6 +196,9 @@
     <t>SK</t>
   </si>
   <si>
+    <t>2024-09-05</t>
+  </si>
+  <si>
     <t>2024-08-26</t>
   </si>
   <si>
@@ -211,6 +220,9 @@
     <t>2024-07-19</t>
   </si>
   <si>
+    <t>2024-09-11</t>
+  </si>
+  <si>
     <t>2024-08-30</t>
   </si>
   <si>
@@ -236,6 +248,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>1004 : 1</t>
   </si>
   <si>
     <t>12.89 : 1</t>
@@ -641,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -711,61 +726,61 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F2">
-        <v>78720000</v>
+        <v>15900000</v>
       </c>
       <c r="G2">
-        <v>2460000</v>
+        <v>7950000</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I2">
-        <v>32000</v>
+        <v>2000</v>
       </c>
       <c r="J2">
-        <v>40200</v>
+        <v>2000</v>
       </c>
       <c r="K2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L2">
-        <v>32000</v>
+        <v>2000</v>
       </c>
       <c r="M2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="S2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -773,123 +788,123 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F3">
-        <v>24000000</v>
+        <v>78720000</v>
       </c>
       <c r="G3">
-        <v>1500000</v>
+        <v>2460000</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I3">
-        <v>11000</v>
+        <v>32000</v>
       </c>
       <c r="J3">
-        <v>13000</v>
+        <v>40200</v>
       </c>
       <c r="K3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L3">
-        <v>16000</v>
+        <v>32000</v>
       </c>
       <c r="M3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="S3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F4">
-        <v>23972040</v>
+        <v>24000000</v>
       </c>
       <c r="G4">
-        <v>1566800</v>
+        <v>1500000</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I4">
-        <v>13600</v>
+        <v>11000</v>
       </c>
       <c r="J4">
-        <v>15300</v>
+        <v>13000</v>
       </c>
       <c r="K4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L4">
-        <v>15300</v>
+        <v>16000</v>
       </c>
       <c r="M4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="S4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -897,123 +912,123 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="F5">
-        <v>13000000</v>
+        <v>23972040</v>
       </c>
       <c r="G5">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I5">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J5">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L5">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="M5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="S5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>13000000</v>
       </c>
       <c r="G6">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="H6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I6">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J6">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L6">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="M6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="S6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1021,123 +1036,123 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F7">
-        <v>50781225</v>
+        <v>13000000</v>
       </c>
       <c r="G7">
-        <v>3077650</v>
+        <v>6500000</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I7">
-        <v>13800</v>
+        <v>2000</v>
       </c>
       <c r="J7">
-        <v>15700</v>
+        <v>2000</v>
       </c>
       <c r="K7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L7">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="M7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="S7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F8">
-        <v>21700000</v>
+        <v>50781225</v>
       </c>
       <c r="G8">
-        <v>1400000</v>
+        <v>3077650</v>
       </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I8">
-        <v>12500</v>
+        <v>13800</v>
       </c>
       <c r="J8">
-        <v>15500</v>
+        <v>15700</v>
       </c>
       <c r="K8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L8">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="M8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="S8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1145,61 +1160,61 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>29000000</v>
+        <v>21700000</v>
       </c>
       <c r="G9">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I9">
-        <v>24000</v>
+        <v>12500</v>
       </c>
       <c r="J9">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L9">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="M9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R9" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="S9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1207,61 +1222,61 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="F10">
-        <v>15771000</v>
+        <v>29000000</v>
       </c>
       <c r="G10">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I10">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J10">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="K10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L10">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="M10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O10">
-        <v>72.87616511318242</v>
+        <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R10" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="S10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1269,123 +1284,123 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F11">
-        <v>11600000</v>
+        <v>15771000</v>
       </c>
       <c r="G11">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I11">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J11">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L11">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="M11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>72.87616511318242</v>
       </c>
       <c r="P11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="S11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
         <v>26</v>
       </c>
-      <c r="B12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="F12">
-        <v>22400000</v>
+        <v>11600000</v>
       </c>
       <c r="G12">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I12">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J12">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L12">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="M12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="S12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1393,61 +1408,61 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F13">
-        <v>22340000</v>
+        <v>22400000</v>
       </c>
       <c r="G13">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I13">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J13">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L13">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="M13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="S13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1455,61 +1470,61 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>29700000</v>
+        <v>22340000</v>
       </c>
       <c r="G14">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I14">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J14">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L14">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="M14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="S14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1517,61 +1532,61 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F15">
-        <v>266000000</v>
+        <v>29700000</v>
       </c>
       <c r="G15">
-        <v>7600000</v>
+        <v>1350000</v>
       </c>
       <c r="H15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I15">
-        <v>24000</v>
+        <v>14000</v>
       </c>
       <c r="J15">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="K15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L15">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="M15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O15">
-        <v>14.47368421052632</v>
+        <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R15" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="S15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1579,61 +1594,61 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F16">
-        <v>12000000</v>
+        <v>266000000</v>
       </c>
       <c r="G16">
-        <v>6000000</v>
+        <v>7600000</v>
       </c>
       <c r="H16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I16">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="J16">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="K16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L16">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="M16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>14.47368421052632</v>
       </c>
       <c r="P16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R16" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="S16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1641,25 +1656,25 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="F17">
-        <v>8000000</v>
+        <v>12000000</v>
       </c>
       <c r="G17">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1668,34 +1683,96 @@
         <v>2000</v>
       </c>
       <c r="K17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L17">
         <v>2000</v>
       </c>
       <c r="M17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R17" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="S17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T17" t="s">
-        <v>73</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18">
+        <v>8000000</v>
+      </c>
+      <c r="G18">
+        <v>4000000</v>
+      </c>
+      <c r="H18" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18">
+        <v>2000</v>
+      </c>
+      <c r="J18">
+        <v>2000</v>
+      </c>
+      <c r="K18" t="s">
+        <v>77</v>
+      </c>
+      <c r="L18">
+        <v>2000</v>
+      </c>
+      <c r="M18" t="s">
+        <v>77</v>
+      </c>
+      <c r="N18" t="s">
+        <v>77</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>77</v>
+      </c>
+      <c r="R18" t="s">
+        <v>94</v>
+      </c>
+      <c r="S18" t="s">
+        <v>77</v>
+      </c>
+      <c r="T18" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="91">
   <si>
     <t>청약일</t>
   </si>
@@ -112,9 +112,6 @@
     <t>2024-07-16</t>
   </si>
   <si>
-    <t>2024-07-15</t>
-  </si>
-  <si>
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
     <t>엔에이치스팩31호</t>
   </si>
   <si>
-    <t>SK증권제13호스팩</t>
-  </si>
-  <si>
     <t>미래</t>
   </si>
   <si>
@@ -193,9 +187,6 @@
     <t>교보</t>
   </si>
   <si>
-    <t>SK</t>
-  </si>
-  <si>
     <t>2024-09-05</t>
   </si>
   <si>
@@ -296,9 +287,6 @@
   </si>
   <si>
     <t>1036 : 1</t>
-  </si>
-  <si>
-    <t>1654.28 : 1</t>
   </si>
 </sst>
 </file>
@@ -656,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -726,16 +714,16 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F2">
         <v>15900000</v>
@@ -744,7 +732,7 @@
         <v>7950000</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I2">
         <v>2000</v>
@@ -753,34 +741,34 @@
         <v>2000</v>
       </c>
       <c r="K2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L2">
         <v>2000</v>
       </c>
       <c r="M2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="S2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -788,16 +776,16 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F3">
         <v>78720000</v>
@@ -806,7 +794,7 @@
         <v>2460000</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I3">
         <v>32000</v>
@@ -815,34 +803,34 @@
         <v>40200</v>
       </c>
       <c r="K3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L3">
         <v>32000</v>
       </c>
       <c r="M3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -850,16 +838,16 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F4">
         <v>24000000</v>
@@ -868,7 +856,7 @@
         <v>1500000</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I4">
         <v>11000</v>
@@ -877,34 +865,34 @@
         <v>13000</v>
       </c>
       <c r="K4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L4">
         <v>16000</v>
       </c>
       <c r="M4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>74</v>
+      </c>
+      <c r="R4" t="s">
         <v>77</v>
       </c>
-      <c r="Q4" t="s">
-        <v>77</v>
-      </c>
-      <c r="R4" t="s">
-        <v>80</v>
-      </c>
       <c r="S4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -912,16 +900,16 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F5">
         <v>23972040</v>
@@ -930,7 +918,7 @@
         <v>1566800</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I5">
         <v>13600</v>
@@ -939,34 +927,34 @@
         <v>15300</v>
       </c>
       <c r="K5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L5">
         <v>15300</v>
       </c>
       <c r="M5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="S5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -974,13 +962,13 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -992,7 +980,7 @@
         <v>1000000</v>
       </c>
       <c r="H6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I6">
         <v>9500</v>
@@ -1001,34 +989,34 @@
         <v>10700</v>
       </c>
       <c r="K6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L6">
         <v>13000</v>
       </c>
       <c r="M6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O6">
         <v>50</v>
       </c>
       <c r="P6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="S6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1036,16 +1024,16 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F7">
         <v>13000000</v>
@@ -1054,7 +1042,7 @@
         <v>6500000</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I7">
         <v>2000</v>
@@ -1063,34 +1051,34 @@
         <v>2000</v>
       </c>
       <c r="K7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L7">
         <v>2000</v>
       </c>
       <c r="M7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="S7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1098,16 +1086,16 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F8">
         <v>50781225</v>
@@ -1116,7 +1104,7 @@
         <v>3077650</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I8">
         <v>13800</v>
@@ -1125,34 +1113,34 @@
         <v>15700</v>
       </c>
       <c r="K8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L8">
         <v>16500</v>
       </c>
       <c r="M8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="S8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1160,16 +1148,16 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F9">
         <v>21700000</v>
@@ -1178,7 +1166,7 @@
         <v>1400000</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I9">
         <v>12500</v>
@@ -1187,34 +1175,34 @@
         <v>15500</v>
       </c>
       <c r="K9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L9">
         <v>15500</v>
       </c>
       <c r="M9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="S9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1222,16 +1210,16 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F10">
         <v>29000000</v>
@@ -1240,7 +1228,7 @@
         <v>1000000</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I10">
         <v>24000</v>
@@ -1249,34 +1237,34 @@
         <v>29000</v>
       </c>
       <c r="K10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L10">
         <v>29000</v>
       </c>
       <c r="M10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="S10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1284,16 +1272,16 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F11">
         <v>15771000</v>
@@ -1302,7 +1290,7 @@
         <v>751000</v>
       </c>
       <c r="H11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I11">
         <v>18000</v>
@@ -1311,34 +1299,34 @@
         <v>21000</v>
       </c>
       <c r="K11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L11">
         <v>21000</v>
       </c>
       <c r="M11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O11">
         <v>72.87616511318242</v>
       </c>
       <c r="P11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1346,16 +1334,16 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F12">
         <v>11600000</v>
@@ -1364,7 +1352,7 @@
         <v>5800000</v>
       </c>
       <c r="H12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I12">
         <v>2000</v>
@@ -1373,34 +1361,34 @@
         <v>2000</v>
       </c>
       <c r="K12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L12">
         <v>2000</v>
       </c>
       <c r="M12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1408,10 +1396,10 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -1426,7 +1414,7 @@
         <v>1400000</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I13">
         <v>16000</v>
@@ -1435,34 +1423,34 @@
         <v>19000</v>
       </c>
       <c r="K13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L13">
         <v>16000</v>
       </c>
       <c r="M13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1470,13 +1458,13 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
         <v>26</v>
@@ -1488,7 +1476,7 @@
         <v>2234000</v>
       </c>
       <c r="H14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I14">
         <v>7300</v>
@@ -1497,34 +1485,34 @@
         <v>8500</v>
       </c>
       <c r="K14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L14">
         <v>10000</v>
       </c>
       <c r="M14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1532,16 +1520,16 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
         <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F15">
         <v>29700000</v>
@@ -1550,7 +1538,7 @@
         <v>1350000</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I15">
         <v>14000</v>
@@ -1559,34 +1547,34 @@
         <v>17000</v>
       </c>
       <c r="K15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L15">
         <v>22000</v>
       </c>
       <c r="M15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="S15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1594,16 +1582,16 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F16">
         <v>266000000</v>
@@ -1612,7 +1600,7 @@
         <v>7600000</v>
       </c>
       <c r="H16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I16">
         <v>24000</v>
@@ -1621,34 +1609,34 @@
         <v>30000</v>
       </c>
       <c r="K16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L16">
         <v>35000</v>
       </c>
       <c r="M16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O16">
         <v>14.47368421052632</v>
       </c>
       <c r="P16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="S16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1656,16 +1644,16 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F17">
         <v>12000000</v>
@@ -1674,7 +1662,7 @@
         <v>6000000</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1683,96 +1671,34 @@
         <v>2000</v>
       </c>
       <c r="K17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L17">
         <v>2000</v>
       </c>
       <c r="M17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R17" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="S17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18">
-        <v>8000000</v>
-      </c>
-      <c r="G18">
-        <v>4000000</v>
-      </c>
-      <c r="H18" t="s">
-        <v>77</v>
-      </c>
-      <c r="I18">
-        <v>2000</v>
-      </c>
-      <c r="J18">
-        <v>2000</v>
-      </c>
-      <c r="K18" t="s">
-        <v>77</v>
-      </c>
-      <c r="L18">
-        <v>2000</v>
-      </c>
-      <c r="M18" t="s">
-        <v>77</v>
-      </c>
-      <c r="N18" t="s">
-        <v>77</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>77</v>
-      </c>
-      <c r="R18" t="s">
-        <v>94</v>
-      </c>
-      <c r="S18" t="s">
-        <v>77</v>
-      </c>
-      <c r="T18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="86">
   <si>
     <t>청약일</t>
   </si>
@@ -109,9 +109,6 @@
     <t>2024-07-18</t>
   </si>
   <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
@@ -157,9 +154,6 @@
     <t>산일전기</t>
   </si>
   <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
     <t>미래</t>
   </si>
   <si>
@@ -208,9 +202,6 @@
     <t>2024-07-23</t>
   </si>
   <si>
-    <t>2024-07-19</t>
-  </si>
-  <si>
     <t>2024-09-11</t>
   </si>
   <si>
@@ -235,9 +226,6 @@
     <t>2024-07-29</t>
   </si>
   <si>
-    <t>2024-07-26</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -284,9 +272,6 @@
   </si>
   <si>
     <t>423.09 : 1</t>
-  </si>
-  <si>
-    <t>1036 : 1</t>
   </si>
 </sst>
 </file>
@@ -644,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -714,16 +699,16 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F2">
         <v>15900000</v>
@@ -732,7 +717,7 @@
         <v>7950000</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I2">
         <v>2000</v>
@@ -741,34 +726,34 @@
         <v>2000</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L2">
         <v>2000</v>
       </c>
       <c r="M2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="S2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -776,16 +761,16 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F3">
         <v>78720000</v>
@@ -794,7 +779,7 @@
         <v>2460000</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I3">
         <v>32000</v>
@@ -803,34 +788,34 @@
         <v>40200</v>
       </c>
       <c r="K3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L3">
         <v>32000</v>
       </c>
       <c r="M3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="S3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -838,16 +823,16 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F4">
         <v>24000000</v>
@@ -856,7 +841,7 @@
         <v>1500000</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I4">
         <v>11000</v>
@@ -865,34 +850,34 @@
         <v>13000</v>
       </c>
       <c r="K4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L4">
         <v>16000</v>
       </c>
       <c r="M4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="S4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -900,16 +885,16 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F5">
         <v>23972040</v>
@@ -918,7 +903,7 @@
         <v>1566800</v>
       </c>
       <c r="H5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I5">
         <v>13600</v>
@@ -927,34 +912,34 @@
         <v>15300</v>
       </c>
       <c r="K5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L5">
         <v>15300</v>
       </c>
       <c r="M5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R5" t="s">
         <v>74</v>
       </c>
-      <c r="Q5" t="s">
-        <v>74</v>
-      </c>
-      <c r="R5" t="s">
-        <v>78</v>
-      </c>
       <c r="S5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -962,13 +947,13 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -980,7 +965,7 @@
         <v>1000000</v>
       </c>
       <c r="H6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I6">
         <v>9500</v>
@@ -989,34 +974,34 @@
         <v>10700</v>
       </c>
       <c r="K6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L6">
         <v>13000</v>
       </c>
       <c r="M6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O6">
         <v>50</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="S6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1024,16 +1009,16 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F7">
         <v>13000000</v>
@@ -1042,7 +1027,7 @@
         <v>6500000</v>
       </c>
       <c r="H7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I7">
         <v>2000</v>
@@ -1051,34 +1036,34 @@
         <v>2000</v>
       </c>
       <c r="K7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L7">
         <v>2000</v>
       </c>
       <c r="M7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="S7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1086,16 +1071,16 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F8">
         <v>50781225</v>
@@ -1104,7 +1089,7 @@
         <v>3077650</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I8">
         <v>13800</v>
@@ -1113,34 +1098,34 @@
         <v>15700</v>
       </c>
       <c r="K8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L8">
         <v>16500</v>
       </c>
       <c r="M8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="S8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1148,16 +1133,16 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F9">
         <v>21700000</v>
@@ -1166,7 +1151,7 @@
         <v>1400000</v>
       </c>
       <c r="H9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I9">
         <v>12500</v>
@@ -1175,34 +1160,34 @@
         <v>15500</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L9">
         <v>15500</v>
       </c>
       <c r="M9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="S9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1210,16 +1195,16 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F10">
         <v>29000000</v>
@@ -1228,7 +1213,7 @@
         <v>1000000</v>
       </c>
       <c r="H10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I10">
         <v>24000</v>
@@ -1237,34 +1222,34 @@
         <v>29000</v>
       </c>
       <c r="K10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L10">
         <v>29000</v>
       </c>
       <c r="M10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="S10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1272,16 +1257,16 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F11">
         <v>15771000</v>
@@ -1290,7 +1275,7 @@
         <v>751000</v>
       </c>
       <c r="H11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I11">
         <v>18000</v>
@@ -1299,34 +1284,34 @@
         <v>21000</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L11">
         <v>21000</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O11">
         <v>72.87616511318242</v>
       </c>
       <c r="P11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1334,16 +1319,16 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F12">
         <v>11600000</v>
@@ -1352,7 +1337,7 @@
         <v>5800000</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I12">
         <v>2000</v>
@@ -1361,34 +1346,34 @@
         <v>2000</v>
       </c>
       <c r="K12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L12">
         <v>2000</v>
       </c>
       <c r="M12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="S12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1396,10 +1381,10 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -1414,7 +1399,7 @@
         <v>1400000</v>
       </c>
       <c r="H13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I13">
         <v>16000</v>
@@ -1423,34 +1408,34 @@
         <v>19000</v>
       </c>
       <c r="K13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L13">
         <v>16000</v>
       </c>
       <c r="M13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1458,13 +1443,13 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>26</v>
@@ -1476,7 +1461,7 @@
         <v>2234000</v>
       </c>
       <c r="H14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I14">
         <v>7300</v>
@@ -1485,34 +1470,34 @@
         <v>8500</v>
       </c>
       <c r="K14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L14">
         <v>10000</v>
       </c>
       <c r="M14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="S14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1520,16 +1505,16 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
         <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F15">
         <v>29700000</v>
@@ -1538,7 +1523,7 @@
         <v>1350000</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I15">
         <v>14000</v>
@@ -1547,34 +1532,34 @@
         <v>17000</v>
       </c>
       <c r="K15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L15">
         <v>22000</v>
       </c>
       <c r="M15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="S15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1582,16 +1567,16 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
         <v>46</v>
       </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F16">
         <v>266000000</v>
@@ -1600,7 +1585,7 @@
         <v>7600000</v>
       </c>
       <c r="H16" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I16">
         <v>24000</v>
@@ -1609,96 +1594,34 @@
         <v>30000</v>
       </c>
       <c r="K16" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L16">
         <v>35000</v>
       </c>
       <c r="M16" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N16" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O16">
         <v>14.47368421052632</v>
       </c>
       <c r="P16" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q16" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R16" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="S16" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="T16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17">
-        <v>12000000</v>
-      </c>
-      <c r="G17">
-        <v>6000000</v>
-      </c>
-      <c r="H17" t="s">
-        <v>74</v>
-      </c>
-      <c r="I17">
-        <v>2000</v>
-      </c>
-      <c r="J17">
-        <v>2000</v>
-      </c>
-      <c r="K17" t="s">
-        <v>74</v>
-      </c>
-      <c r="L17">
-        <v>2000</v>
-      </c>
-      <c r="M17" t="s">
-        <v>74</v>
-      </c>
-      <c r="N17" t="s">
-        <v>74</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>74</v>
-      </c>
-      <c r="R17" t="s">
-        <v>90</v>
-      </c>
-      <c r="S17" t="s">
-        <v>74</v>
-      </c>
-      <c r="T17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="81">
   <si>
     <t>청약일</t>
   </si>
@@ -106,9 +106,6 @@
     <t>2024-07-22</t>
   </si>
   <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
@@ -151,9 +148,6 @@
     <t>피앤에스미캐닉스</t>
   </si>
   <si>
-    <t>산일전기</t>
-  </si>
-  <si>
     <t>미래</t>
   </si>
   <si>
@@ -199,9 +193,6 @@
     <t>2024-07-30</t>
   </si>
   <si>
-    <t>2024-07-23</t>
-  </si>
-  <si>
     <t>2024-09-11</t>
   </si>
   <si>
@@ -223,9 +214,6 @@
     <t>2024-07-31</t>
   </si>
   <si>
-    <t>2024-07-29</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -269,9 +257,6 @@
   </si>
   <si>
     <t>1585.92 : 1</t>
-  </si>
-  <si>
-    <t>423.09 : 1</t>
   </si>
 </sst>
 </file>
@@ -629,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -699,16 +684,16 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F2">
         <v>15900000</v>
@@ -717,7 +702,7 @@
         <v>7950000</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I2">
         <v>2000</v>
@@ -726,34 +711,34 @@
         <v>2000</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L2">
         <v>2000</v>
       </c>
       <c r="M2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="S2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -761,16 +746,16 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F3">
         <v>78720000</v>
@@ -779,7 +764,7 @@
         <v>2460000</v>
       </c>
       <c r="H3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I3">
         <v>32000</v>
@@ -788,34 +773,34 @@
         <v>40200</v>
       </c>
       <c r="K3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L3">
         <v>32000</v>
       </c>
       <c r="M3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="S3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -823,16 +808,16 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F4">
         <v>24000000</v>
@@ -841,7 +826,7 @@
         <v>1500000</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I4">
         <v>11000</v>
@@ -850,34 +835,34 @@
         <v>13000</v>
       </c>
       <c r="K4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L4">
         <v>16000</v>
       </c>
       <c r="M4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="S4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -885,16 +870,16 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F5">
         <v>23972040</v>
@@ -903,7 +888,7 @@
         <v>1566800</v>
       </c>
       <c r="H5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I5">
         <v>13600</v>
@@ -912,34 +897,34 @@
         <v>15300</v>
       </c>
       <c r="K5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L5">
         <v>15300</v>
       </c>
       <c r="M5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R5" t="s">
         <v>70</v>
       </c>
-      <c r="Q5" t="s">
-        <v>70</v>
-      </c>
-      <c r="R5" t="s">
-        <v>74</v>
-      </c>
       <c r="S5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -947,13 +932,13 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -965,7 +950,7 @@
         <v>1000000</v>
       </c>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I6">
         <v>9500</v>
@@ -974,34 +959,34 @@
         <v>10700</v>
       </c>
       <c r="K6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L6">
         <v>13000</v>
       </c>
       <c r="M6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O6">
         <v>50</v>
       </c>
       <c r="P6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="S6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1009,16 +994,16 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F7">
         <v>13000000</v>
@@ -1027,7 +1012,7 @@
         <v>6500000</v>
       </c>
       <c r="H7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I7">
         <v>2000</v>
@@ -1036,34 +1021,34 @@
         <v>2000</v>
       </c>
       <c r="K7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L7">
         <v>2000</v>
       </c>
       <c r="M7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="S7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1071,16 +1056,16 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F8">
         <v>50781225</v>
@@ -1089,7 +1074,7 @@
         <v>3077650</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I8">
         <v>13800</v>
@@ -1098,34 +1083,34 @@
         <v>15700</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L8">
         <v>16500</v>
       </c>
       <c r="M8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="S8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1133,16 +1118,16 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F9">
         <v>21700000</v>
@@ -1151,7 +1136,7 @@
         <v>1400000</v>
       </c>
       <c r="H9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I9">
         <v>12500</v>
@@ -1160,34 +1145,34 @@
         <v>15500</v>
       </c>
       <c r="K9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L9">
         <v>15500</v>
       </c>
       <c r="M9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="S9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1195,16 +1180,16 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F10">
         <v>29000000</v>
@@ -1213,7 +1198,7 @@
         <v>1000000</v>
       </c>
       <c r="H10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I10">
         <v>24000</v>
@@ -1222,34 +1207,34 @@
         <v>29000</v>
       </c>
       <c r="K10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L10">
         <v>29000</v>
       </c>
       <c r="M10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="S10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1257,16 +1242,16 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F11">
         <v>15771000</v>
@@ -1275,7 +1260,7 @@
         <v>751000</v>
       </c>
       <c r="H11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I11">
         <v>18000</v>
@@ -1284,34 +1269,34 @@
         <v>21000</v>
       </c>
       <c r="K11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L11">
         <v>21000</v>
       </c>
       <c r="M11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O11">
         <v>72.87616511318242</v>
       </c>
       <c r="P11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="S11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1319,16 +1304,16 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F12">
         <v>11600000</v>
@@ -1337,7 +1322,7 @@
         <v>5800000</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I12">
         <v>2000</v>
@@ -1346,34 +1331,34 @@
         <v>2000</v>
       </c>
       <c r="K12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L12">
         <v>2000</v>
       </c>
       <c r="M12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="S12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1381,10 +1366,10 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -1399,7 +1384,7 @@
         <v>1400000</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I13">
         <v>16000</v>
@@ -1408,34 +1393,34 @@
         <v>19000</v>
       </c>
       <c r="K13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L13">
         <v>16000</v>
       </c>
       <c r="M13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="S13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1443,13 +1428,13 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
         <v>26</v>
@@ -1461,7 +1446,7 @@
         <v>2234000</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I14">
         <v>7300</v>
@@ -1470,34 +1455,34 @@
         <v>8500</v>
       </c>
       <c r="K14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L14">
         <v>10000</v>
       </c>
       <c r="M14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R14" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="S14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1505,16 +1490,16 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
         <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F15">
         <v>29700000</v>
@@ -1523,7 +1508,7 @@
         <v>1350000</v>
       </c>
       <c r="H15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I15">
         <v>14000</v>
@@ -1532,96 +1517,34 @@
         <v>17000</v>
       </c>
       <c r="K15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L15">
         <v>22000</v>
       </c>
       <c r="M15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16">
-        <v>266000000</v>
-      </c>
-      <c r="G16">
-        <v>7600000</v>
-      </c>
-      <c r="H16" t="s">
-        <v>70</v>
-      </c>
-      <c r="I16">
-        <v>24000</v>
-      </c>
-      <c r="J16">
-        <v>30000</v>
-      </c>
-      <c r="K16" t="s">
-        <v>70</v>
-      </c>
-      <c r="L16">
-        <v>35000</v>
-      </c>
-      <c r="M16" t="s">
-        <v>70</v>
-      </c>
-      <c r="N16" t="s">
-        <v>70</v>
-      </c>
-      <c r="O16">
-        <v>14.47368421052632</v>
-      </c>
-      <c r="P16" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>70</v>
-      </c>
-      <c r="R16" t="s">
-        <v>85</v>
-      </c>
-      <c r="S16" t="s">
-        <v>70</v>
-      </c>
-      <c r="T16" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="82">
   <si>
     <t>청약일</t>
   </si>
@@ -76,6 +76,9 @@
     <t>수수료율</t>
   </si>
   <si>
+    <t>2024-09-09</t>
+  </si>
+  <si>
     <t>2024-09-02</t>
   </si>
   <si>
@@ -103,7 +106,7 @@
     <t>2024-07-25</t>
   </si>
   <si>
-    <t>2024-07-22</t>
+    <t>아이언디바이스</t>
   </si>
   <si>
     <t>미래에셋비전스팩7호</t>
@@ -145,7 +148,7 @@
     <t>아이빔테크놀로지</t>
   </si>
   <si>
-    <t>피앤에스미캐닉스</t>
+    <t>대신</t>
   </si>
   <si>
     <t>미래</t>
@@ -163,9 +166,6 @@
     <t>한국</t>
   </si>
   <si>
-    <t>대신</t>
-  </si>
-  <si>
     <t>하나</t>
   </si>
   <si>
@@ -175,6 +175,9 @@
     <t>교보</t>
   </si>
   <si>
+    <t>2024-09-12</t>
+  </si>
+  <si>
     <t>2024-09-05</t>
   </si>
   <si>
@@ -193,6 +196,9 @@
     <t>2024-07-30</t>
   </si>
   <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
     <t>2024-09-11</t>
   </si>
   <si>
@@ -211,12 +217,12 @@
     <t>2024-08-20</t>
   </si>
   <si>
-    <t>2024-07-31</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
+    <t>1965.03 : 1</t>
+  </si>
+  <si>
     <t>1004 : 1</t>
   </si>
   <si>
@@ -254,9 +260,6 @@
   </si>
   <si>
     <t>1094.66 : 1</t>
-  </si>
-  <si>
-    <t>1585.92 : 1</t>
   </si>
 </sst>
 </file>
@@ -693,52 +696,52 @@
         <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F2">
-        <v>15900000</v>
+        <v>21000000</v>
       </c>
       <c r="G2">
-        <v>7950000</v>
+        <v>3000000</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I2">
-        <v>2000</v>
+        <v>4900</v>
       </c>
       <c r="J2">
-        <v>2000</v>
+        <v>5700</v>
       </c>
       <c r="K2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L2">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="M2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -755,52 +758,52 @@
         <v>54</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3">
-        <v>78720000</v>
+        <v>15900000</v>
       </c>
       <c r="G3">
-        <v>2460000</v>
+        <v>7950000</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I3">
-        <v>32000</v>
+        <v>2000</v>
       </c>
       <c r="J3">
-        <v>40200</v>
+        <v>2000</v>
       </c>
       <c r="K3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L3">
-        <v>32000</v>
+        <v>2000</v>
       </c>
       <c r="M3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="S3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -817,57 +820,57 @@
         <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F4">
-        <v>24000000</v>
+        <v>78720000</v>
       </c>
       <c r="G4">
-        <v>1500000</v>
+        <v>2460000</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I4">
-        <v>11000</v>
+        <v>32000</v>
       </c>
       <c r="J4">
-        <v>13000</v>
+        <v>40200</v>
       </c>
       <c r="K4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L4">
-        <v>16000</v>
+        <v>32000</v>
       </c>
       <c r="M4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
@@ -876,55 +879,55 @@
         <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F5">
-        <v>23972040</v>
+        <v>24000000</v>
       </c>
       <c r="G5">
-        <v>1566800</v>
+        <v>1500000</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I5">
-        <v>13600</v>
+        <v>11000</v>
       </c>
       <c r="J5">
-        <v>15300</v>
+        <v>13000</v>
       </c>
       <c r="K5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L5">
-        <v>15300</v>
+        <v>16000</v>
       </c>
       <c r="M5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -941,57 +944,57 @@
         <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="F6">
-        <v>13000000</v>
+        <v>23972040</v>
       </c>
       <c r="G6">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I6">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J6">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L6">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="M6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
         <v>35</v>
@@ -1000,55 +1003,55 @@
         <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>13000000</v>
       </c>
       <c r="G7">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I7">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J7">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L7">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="M7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1068,111 +1071,111 @@
         <v>63</v>
       </c>
       <c r="F8">
-        <v>50781225</v>
+        <v>13000000</v>
       </c>
       <c r="G8">
-        <v>3077650</v>
+        <v>6500000</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I8">
-        <v>13800</v>
+        <v>2000</v>
       </c>
       <c r="J8">
-        <v>15700</v>
+        <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L8">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="M8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F9">
-        <v>21700000</v>
+        <v>50781225</v>
       </c>
       <c r="G9">
-        <v>1400000</v>
+        <v>3077650</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I9">
-        <v>12500</v>
+        <v>13800</v>
       </c>
       <c r="J9">
-        <v>15500</v>
+        <v>15700</v>
       </c>
       <c r="K9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L9">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="M9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1183,58 +1186,58 @@
         <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F10">
-        <v>29000000</v>
+        <v>21700000</v>
       </c>
       <c r="G10">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I10">
-        <v>24000</v>
+        <v>12500</v>
       </c>
       <c r="J10">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L10">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="M10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1245,58 +1248,58 @@
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F11">
-        <v>15771000</v>
+        <v>29000000</v>
       </c>
       <c r="G11">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I11">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J11">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="K11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L11">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="M11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O11">
-        <v>72.87616511318242</v>
+        <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1307,120 +1310,120 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12">
-        <v>11600000</v>
+        <v>15771000</v>
       </c>
       <c r="G12">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I12">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J12">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L12">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="M12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>72.87616511318242</v>
       </c>
       <c r="P12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="F13">
-        <v>22400000</v>
+        <v>11600000</v>
       </c>
       <c r="G13">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I13">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J13">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L13">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="M13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1434,55 +1437,55 @@
         <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>22340000</v>
+        <v>22400000</v>
       </c>
       <c r="G14">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I14">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J14">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L14">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="M14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1493,58 +1496,58 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="F15">
-        <v>29700000</v>
+        <v>22340000</v>
       </c>
       <c r="G15">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I15">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J15">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L15">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="M15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form2.xlsx
+++ b/datasets/form2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="88">
   <si>
     <t>청약일</t>
   </si>
@@ -76,6 +76,9 @@
     <t>수수료율</t>
   </si>
   <si>
+    <t>2024-09-10</t>
+  </si>
+  <si>
     <t>2024-09-09</t>
   </si>
   <si>
@@ -106,6 +109,9 @@
     <t>2024-07-25</t>
   </si>
   <si>
+    <t>KB제30호스팩</t>
+  </si>
+  <si>
     <t>아이언디바이스</t>
   </si>
   <si>
@@ -148,6 +154,9 @@
     <t>아이빔테크놀로지</t>
   </si>
   <si>
+    <t>KB</t>
+  </si>
+  <si>
     <t>대신</t>
   </si>
   <si>
@@ -175,6 +184,9 @@
     <t>교보</t>
   </si>
   <si>
+    <t>2024-09-13</t>
+  </si>
+  <si>
     <t>2024-09-12</t>
   </si>
   <si>
@@ -196,6 +208,9 @@
     <t>2024-07-30</t>
   </si>
   <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
     <t>2024-09-23</t>
   </si>
   <si>
@@ -218,6 +233,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>619.62 : 1</t>
   </si>
   <si>
     <t>1965.03 : 1</t>
@@ -617,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -687,61 +705,61 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F2">
-        <v>21000000</v>
+        <v>10000000</v>
       </c>
       <c r="G2">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I2">
-        <v>4900</v>
+        <v>2000</v>
       </c>
       <c r="J2">
-        <v>5700</v>
+        <v>2000</v>
       </c>
       <c r="K2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L2">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="M2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="S2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -749,61 +767,61 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F3">
-        <v>15900000</v>
+        <v>21000000</v>
       </c>
       <c r="G3">
-        <v>7950000</v>
+        <v>3000000</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I3">
-        <v>2000</v>
+        <v>4900</v>
       </c>
       <c r="J3">
-        <v>2000</v>
+        <v>5700</v>
       </c>
       <c r="K3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L3">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="M3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="S3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -811,61 +829,61 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F4">
-        <v>78720000</v>
+        <v>15900000</v>
       </c>
       <c r="G4">
-        <v>2460000</v>
+        <v>7950000</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I4">
-        <v>32000</v>
+        <v>2000</v>
       </c>
       <c r="J4">
-        <v>40200</v>
+        <v>2000</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L4">
-        <v>32000</v>
+        <v>2000</v>
       </c>
       <c r="M4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -873,123 +891,123 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F5">
-        <v>24000000</v>
+        <v>78720000</v>
       </c>
       <c r="G5">
-        <v>1500000</v>
+        <v>2460000</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I5">
-        <v>11000</v>
+        <v>32000</v>
       </c>
       <c r="J5">
-        <v>13000</v>
+        <v>40200</v>
       </c>
       <c r="K5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L5">
-        <v>16000</v>
+        <v>32000</v>
       </c>
       <c r="M5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="S5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F6">
-        <v>23972040</v>
+        <v>24000000</v>
       </c>
       <c r="G6">
-        <v>1566800</v>
+        <v>1500000</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I6">
-        <v>13600</v>
+        <v>11000</v>
       </c>
       <c r="J6">
-        <v>15300</v>
+        <v>13000</v>
       </c>
       <c r="K6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L6">
-        <v>15300</v>
+        <v>16000</v>
       </c>
       <c r="M6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="S6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -997,123 +1015,123 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="F7">
-        <v>13000000</v>
+        <v>23972040</v>
       </c>
       <c r="G7">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I7">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J7">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L7">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="M7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="S7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="F8">
         <v>13000000</v>
       </c>
       <c r="G8">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I8">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J8">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L8">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="M8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="S8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1121,123 +1139,123 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F9">
-        <v>50781225</v>
+        <v>13000000</v>
       </c>
       <c r="G9">
-        <v>3077650</v>
+        <v>6500000</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I9">
-        <v>13800</v>
+        <v>2000</v>
       </c>
       <c r="J9">
-        <v>15700</v>
+        <v>2000</v>
       </c>
       <c r="K9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L9">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="M9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R9" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F10">
-        <v>21700000</v>
+        <v>50781225</v>
       </c>
       <c r="G10">
-        <v>1400000</v>
+        <v>3077650</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I10">
-        <v>12500</v>
+        <v>13800</v>
       </c>
       <c r="J10">
-        <v>15500</v>
+        <v>15700</v>
       </c>
       <c r="K10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L10">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="M10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R10" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="S10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1245,61 +1263,61 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F11">
-        <v>29000000</v>
+        <v>21700000</v>
       </c>
       <c r="G11">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I11">
-        <v>24000</v>
+        <v>12500</v>
       </c>
       <c r="J11">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L11">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="M11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="S11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1307,61 +1325,61 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F12">
-        <v>15771000</v>
+        <v>29000000</v>
       </c>
       <c r="G12">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="H12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I12">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J12">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="K12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L12">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="M12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O12">
-        <v>72.87616511318242</v>
+        <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="S12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1369,123 +1387,123 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F13">
-        <v>11600000</v>
+        <v>15771000</v>
       </c>
       <c r="G13">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I13">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J13">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L13">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="M13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>72.87616511318242</v>
       </c>
       <c r="P13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R13" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="S13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
         <v>28</v>
       </c>
-      <c r="B14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>27</v>
-      </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F14">
-        <v>22400000</v>
+        <v>11600000</v>
       </c>
       <c r="G14">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I14">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J14">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L14">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="M14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R14" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="S14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1493,61 +1511,123 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F15">
-        <v>22340000</v>
+        <v>22400000</v>
       </c>
       <c r="G15">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I15">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J15">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L15">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="M15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R15" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="S15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T15" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16">
+        <v>22340000</v>
+      </c>
+      <c r="G16">
+        <v>2234000</v>
+      </c>
+      <c r="H16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16">
+        <v>7300</v>
+      </c>
+      <c r="J16">
+        <v>8500</v>
+      </c>
+      <c r="K16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L16">
+        <v>10000</v>
+      </c>
+      <c r="M16" t="s">
+        <v>72</v>
+      </c>
+      <c r="N16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>72</v>
+      </c>
+      <c r="R16" t="s">
+        <v>87</v>
+      </c>
+      <c r="S16" t="s">
+        <v>72</v>
+      </c>
+      <c r="T16" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
